--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-05.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H2" t="n">
         <v>1.68</v>
       </c>
       <c r="I2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
@@ -799,7 +799,7 @@
         <v>2.76</v>
       </c>
       <c r="T2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U2" t="n">
         <v>2.18</v>
@@ -820,19 +820,19 @@
         <v>12</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AB2" t="n">
         <v>22</v>
       </c>
       <c r="AC2" t="n">
-        <v>48</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF2" t="n">
         <v>44</v>
@@ -841,7 +841,7 @@
         <v>21</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI2" t="n">
         <v>32</v>
@@ -865,7 +865,7 @@
         <v>10</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>9</v>
@@ -874,10 +874,10 @@
         <v>10</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU2" t="n">
         <v>8.4</v>
@@ -889,38 +889,38 @@
         <v>13</v>
       </c>
       <c r="AX2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>6.6</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BA2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BC2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -951,76 +951,76 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I3" t="n">
         <v>6.2</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V3" t="n">
         <v>1.19</v>
       </c>
       <c r="W3" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="X3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD3" t="n">
         <v>25</v>
@@ -1029,92 +1029,92 @@
         <v>80</v>
       </c>
       <c r="AF3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
         <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL3" t="n">
         <v>26</v>
       </c>
       <c r="AM3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AO3" t="n">
         <v>55</v>
       </c>
       <c r="AP3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>20</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AR3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT3" t="n">
         <v>10.5</v>
       </c>
       <c r="AU3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX3" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>11</v>
       </c>
       <c r="AY3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="G6" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="J6" t="n">
         <v>3.95</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>2.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1590,13 +1590,13 @@
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB6" t="n">
         <v>1000</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1641,16 +1641,16 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR6" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AS6" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT6" t="n">
         <v>10.5</v>
@@ -1659,28 +1659,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
         <v>27</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ6" t="n">
         <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD6" t="n">
         <v>20</v>
@@ -1689,14 +1689,14 @@
         <v>44</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG6" t="n">
         <v>19</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H7" t="n">
         <v>3.65</v>
@@ -1742,7 +1742,7 @@
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1781,13 +1781,13 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="n">
         <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
@@ -1802,7 +1802,7 @@
         <v>17</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF7" t="n">
         <v>14</v>
@@ -1841,10 +1841,10 @@
         <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT7" t="n">
         <v>8.199999999999999</v>
@@ -1856,7 +1856,7 @@
         <v>13.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX7" t="n">
         <v>11</v>
@@ -1868,10 +1868,10 @@
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC7" t="n">
         <v>19</v>
@@ -1880,17 +1880,17 @@
         <v>30</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF7" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
         <v>3.05</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q8" t="n">
         <v>2.16</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
         <v>4.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
         <v>4.1</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G12" t="n">
         <v>2.46</v>
@@ -2706,7 +2706,7 @@
         <v>3.05</v>
       </c>
       <c r="I12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="I13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>3.9</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>8.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2915,22 +2915,22 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="O13" t="n">
         <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R13" t="n">
         <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -2939,10 +2939,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="H14" t="n">
         <v>5.1</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q14" t="n">
         <v>2.32</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
         <v>2.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3515,10 +3515,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z16" t="n">
         <v>11.5</v>
@@ -3545,10 +3545,10 @@
         <v>9.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF16" t="n">
         <v>44</v>
@@ -3563,13 +3563,13 @@
         <v>38</v>
       </c>
       <c r="AJ16" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AK16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM16" t="n">
         <v>130</v>
@@ -3581,16 +3581,16 @@
         <v>12</v>
       </c>
       <c r="AP16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>7.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AT16" t="n">
         <v>15</v>
@@ -3605,38 +3605,38 @@
         <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AZ16" t="n">
         <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G18" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="H18" t="n">
         <v>7.6</v>
       </c>
       <c r="I18" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K18" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="G19" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="H19" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I19" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="G20" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="H20" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="I20" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G21" t="n">
         <v>1.56</v>
@@ -4452,7 +4452,7 @@
         <v>5.9</v>
       </c>
       <c r="I21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J21" t="n">
         <v>5</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q21" t="n">
         <v>1.45</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q22" t="n">
         <v>1.45</v>
@@ -4739,7 +4739,7 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO22" t="n">
         <v>5.1</v>
@@ -4769,7 +4769,7 @@
         <v>10.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY22" t="n">
         <v>21</v>
@@ -4781,13 +4781,13 @@
         <v>19.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC22" t="n">
         <v>55</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE22" t="n">
         <v>50</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G23" t="n">
         <v>3.65</v>
       </c>
       <c r="H23" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I23" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -5028,10 +5028,10 @@
         <v>6.6</v>
       </c>
       <c r="G24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H24" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I24" t="n">
         <v>1.55</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G25" t="n">
         <v>3.85</v>
       </c>
       <c r="H25" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I25" t="n">
         <v>2.22</v>
@@ -5234,7 +5234,7 @@
         <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
         <v>1.88</v>
       </c>
       <c r="J26" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K26" t="n">
         <v>3.75</v>
@@ -5443,7 +5443,7 @@
         <v>1.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q26" t="n">
         <v>2.18</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y26" t="n">
         <v>7.6</v>
@@ -5482,7 +5482,7 @@
         <v>16.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD26" t="n">
         <v>10.5</v>
@@ -5509,7 +5509,7 @@
         <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM26" t="n">
         <v>180</v>
@@ -5545,7 +5545,7 @@
         <v>19</v>
       </c>
       <c r="AX26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY26" t="n">
         <v>18.5</v>
@@ -5554,29 +5554,29 @@
         <v>19.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BB26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC26" t="n">
         <v>12</v>
       </c>
-      <c r="BC26" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BD26" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG26" t="n">
         <v>14</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -5610,10 +5610,10 @@
         <v>1.54</v>
       </c>
       <c r="G27" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
         <v>12</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -5804,10 +5804,10 @@
         <v>5.8</v>
       </c>
       <c r="G28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H28" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I28" t="n">
         <v>1.69</v>
@@ -5816,7 +5816,7 @@
         <v>4.1</v>
       </c>
       <c r="K28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
         <v>1.75</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
         <v>420</v>
       </c>
       <c r="H31" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="I31" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="J31" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K31" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -6413,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q31" t="n">
         <v>2.08</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="G33" t="n">
         <v>2.86</v>
       </c>
       <c r="H33" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>970</v>
       </c>
       <c r="J33" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="K33" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -6819,7 +6819,7 @@
         <v>1.9</v>
       </c>
       <c r="V33" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W33" t="n">
         <v>1.53</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G34" t="n">
         <v>2.62</v>
@@ -6974,7 +6974,7 @@
         <v>3.3</v>
       </c>
       <c r="I34" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="J34" t="n">
         <v>3.05</v>
@@ -6989,7 +6989,7 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O34" t="n">
         <v>1.46</v>
@@ -6998,7 +6998,7 @@
         <v>1.61</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R34" t="n">
         <v>1.17</v>
@@ -7013,7 +7013,7 @@
         <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W34" t="n">
         <v>1.65</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -7162,19 +7162,19 @@
         <v>1.8</v>
       </c>
       <c r="G35" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="H35" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I35" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J35" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K35" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7192,13 +7192,13 @@
         <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S35" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -7210,7 +7210,7 @@
         <v>1.25</v>
       </c>
       <c r="W35" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G36" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="H36" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I36" t="n">
         <v>5.2</v>
       </c>
       <c r="J36" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K36" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -7383,7 +7383,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q36" t="n">
         <v>1.86</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G37" t="n">
         <v>2.72</v>
@@ -7628,7 +7628,7 @@
         <v>19</v>
       </c>
       <c r="AG37" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH37" t="n">
         <v>17</v>
@@ -7664,7 +7664,7 @@
         <v>17.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT37" t="n">
         <v>10</v>
@@ -7676,7 +7676,7 @@
         <v>11</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX37" t="n">
         <v>15</v>
@@ -7700,7 +7700,7 @@
         <v>30</v>
       </c>
       <c r="BE37" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF37" t="n">
         <v>17</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -7747,13 +7747,13 @@
         <v>2.84</v>
       </c>
       <c r="H38" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I38" t="n">
         <v>3.25</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K38" t="n">
         <v>3.65</v>
@@ -7771,10 +7771,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="G39" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="H39" t="n">
         <v>6.4</v>
       </c>
       <c r="I39" t="n">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="J39" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="K39" t="n">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -7965,10 +7965,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <v>4.6</v>
       </c>
       <c r="G40" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H40" t="n">
         <v>1.69</v>
@@ -8141,7 +8141,7 @@
         <v>1.75</v>
       </c>
       <c r="J40" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K40" t="n">
         <v>4.7</v>
@@ -8159,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q40" t="n">
         <v>1.67</v>
@@ -8174,7 +8174,7 @@
         <v>1.69</v>
       </c>
       <c r="U40" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
         <v>14.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB40" t="n">
         <v>25</v>
@@ -8219,10 +8219,10 @@
         <v>36</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AL40" t="n">
         <v>70</v>
@@ -8237,7 +8237,7 @@
         <v>10.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ40" t="n">
         <v>7.8</v>
@@ -8246,7 +8246,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS40" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT40" t="n">
         <v>15</v>
@@ -8282,7 +8282,7 @@
         <v>4.1</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF40" t="n">
         <v>4.1</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -8326,16 +8326,16 @@
         <v>2.62</v>
       </c>
       <c r="G41" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H41" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I41" t="n">
         <v>3.25</v>
       </c>
       <c r="J41" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K41" t="n">
         <v>3.3</v>
@@ -8386,7 +8386,7 @@
         <v>21</v>
       </c>
       <c r="AA41" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB41" t="n">
         <v>9</v>
@@ -8452,7 +8452,7 @@
         <v>12</v>
       </c>
       <c r="AW41" t="n">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="AX41" t="n">
         <v>14.5</v>
@@ -8473,20 +8473,20 @@
         <v>29</v>
       </c>
       <c r="BD41" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BE41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF41" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG41" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -8526,10 +8526,10 @@
         <v>2.6</v>
       </c>
       <c r="I42" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J42" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K42" t="n">
         <v>3.55</v>
@@ -8571,7 +8571,7 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y42" t="n">
         <v>9.4</v>
@@ -8634,7 +8634,7 @@
         <v>14.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT42" t="n">
         <v>9.6</v>
@@ -8646,7 +8646,7 @@
         <v>11</v>
       </c>
       <c r="AW42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX42" t="n">
         <v>17.5</v>
@@ -8658,13 +8658,13 @@
         <v>17</v>
       </c>
       <c r="BA42" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB42" t="n">
         <v>38</v>
       </c>
       <c r="BC42" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BD42" t="n">
         <v>40</v>
@@ -8673,14 +8673,14 @@
         <v>11.5</v>
       </c>
       <c r="BF42" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
         <v>2.16</v>
       </c>
       <c r="R43" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -8783,7 +8783,7 @@
         <v>8</v>
       </c>
       <c r="AD43" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE43" t="n">
         <v>1000</v>
@@ -8825,10 +8825,10 @@
         <v>10.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="AT43" t="n">
         <v>8.199999999999999</v>
@@ -8864,17 +8864,17 @@
         <v>8.6</v>
       </c>
       <c r="BE43" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF43" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG43" t="n">
         <v>38</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ44" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA44" t="n">
         <v>36</v>
@@ -9061,14 +9061,14 @@
         <v>32</v>
       </c>
       <c r="BF44" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG44" t="n">
         <v>28</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9105,7 @@
         <v>6.8</v>
       </c>
       <c r="H45" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="I45" t="n">
         <v>1.58</v>
@@ -9180,7 +9180,7 @@
         <v>1000</v>
       </c>
       <c r="AG45" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH45" t="n">
         <v>1000</v>
@@ -9216,7 +9216,7 @@
         <v>5.6</v>
       </c>
       <c r="AS45" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT45" t="n">
         <v>7.4</v>
@@ -9225,25 +9225,25 @@
         <v>5.6</v>
       </c>
       <c r="AV45" t="n">
-        <v>9.4</v>
+        <v>5.2</v>
       </c>
       <c r="AW45" t="n">
         <v>6</v>
       </c>
       <c r="AX45" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY45" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AZ45" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA45" t="n">
         <v>7.2</v>
       </c>
       <c r="BB45" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC45" t="n">
         <v>46</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -9293,13 +9293,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="G46" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H46" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="I46" t="n">
         <v>3.05</v>
@@ -9308,7 +9308,7 @@
         <v>2.86</v>
       </c>
       <c r="K46" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -9487,22 +9487,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G47" t="n">
         <v>5.8</v>
       </c>
       <c r="H47" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="I47" t="n">
         <v>2.18</v>
       </c>
       <c r="J47" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K47" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -9517,7 +9517,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q47" t="n">
         <v>1.5</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -9684,10 +9684,10 @@
         <v>3.3</v>
       </c>
       <c r="G48" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H48" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I48" t="n">
         <v>2.66</v>
@@ -9696,7 +9696,7 @@
         <v>3.1</v>
       </c>
       <c r="K48" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -9744,13 +9744,13 @@
         <v>16</v>
       </c>
       <c r="AA48" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB48" t="n">
         <v>10.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD48" t="n">
         <v>12.5</v>
@@ -9759,7 +9759,7 @@
         <v>36</v>
       </c>
       <c r="AF48" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG48" t="n">
         <v>14.5</v>
@@ -9771,7 +9771,7 @@
         <v>65</v>
       </c>
       <c r="AJ48" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK48" t="n">
         <v>48</v>
@@ -9780,13 +9780,13 @@
         <v>65</v>
       </c>
       <c r="AM48" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN48" t="n">
         <v>55</v>
       </c>
       <c r="AO48" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP48" t="n">
         <v>9.199999999999999</v>
@@ -9810,7 +9810,7 @@
         <v>11</v>
       </c>
       <c r="AW48" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AX48" t="n">
         <v>18.5</v>
@@ -9825,10 +9825,10 @@
         <v>30</v>
       </c>
       <c r="BB48" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BC48" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BD48" t="n">
         <v>50</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G49" t="n">
         <v>1.97</v>
@@ -9890,7 +9890,7 @@
         <v>2.66</v>
       </c>
       <c r="K49" t="n">
-        <v>5.3</v>
+        <v>950</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -9905,7 +9905,7 @@
         <v>1.39</v>
       </c>
       <c r="P49" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="Q49" t="n">
         <v>2</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
         <v>1.5</v>
       </c>
       <c r="G50" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H50" t="n">
         <v>6.4</v>
@@ -10084,7 +10084,7 @@
         <v>4.8</v>
       </c>
       <c r="K50" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -10099,10 +10099,10 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U50" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -10123,13 +10123,13 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Y50" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Z50" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA50" t="n">
         <v>200</v>
@@ -10138,19 +10138,19 @@
         <v>15.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD50" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AE50" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF50" t="n">
         <v>14.5</v>
       </c>
       <c r="AG50" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH50" t="n">
         <v>23</v>
@@ -10159,34 +10159,34 @@
         <v>1000</v>
       </c>
       <c r="AJ50" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK50" t="n">
         <v>18</v>
       </c>
       <c r="AL50" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM50" t="n">
         <v>1000</v>
       </c>
       <c r="AN50" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO50" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP50" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="AR50" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AS50" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AT50" t="n">
         <v>10.5</v>
@@ -10198,7 +10198,7 @@
         <v>19</v>
       </c>
       <c r="AW50" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX50" t="n">
         <v>10</v>
@@ -10210,29 +10210,29 @@
         <v>16</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BB50" t="n">
         <v>12.5</v>
       </c>
       <c r="BC50" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD50" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BE50" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF50" t="n">
         <v>4.5</v>
       </c>
       <c r="BG50" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10278,7 @@
         <v>2.92</v>
       </c>
       <c r="K51" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="G52" t="n">
         <v>1.71</v>
@@ -10466,13 +10466,13 @@
         <v>5.6</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K52" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -10487,10 +10487,10 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -10660,10 +10660,10 @@
         <v>6.6</v>
       </c>
       <c r="I53" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J53" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="K53" t="n">
         <v>6.4</v>
@@ -10684,7 +10684,7 @@
         <v>2.72</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -11621,22 +11621,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="G58" t="n">
         <v>4.2</v>
       </c>
       <c r="H58" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="I58" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="J58" t="n">
         <v>3.2</v>
       </c>
       <c r="K58" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -12009,22 +12009,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="G60" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="H60" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="I60" t="n">
         <v>1.98</v>
       </c>
       <c r="J60" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K60" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -12042,7 +12042,7 @@
         <v>2.04</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -12203,13 +12203,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G61" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H61" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I61" t="n">
         <v>5</v>
@@ -12218,7 +12218,7 @@
         <v>3.15</v>
       </c>
       <c r="K61" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -12233,10 +12233,10 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -12397,22 +12397,22 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G62" t="n">
         <v>2.66</v>
       </c>
       <c r="H62" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I62" t="n">
         <v>4</v>
       </c>
       <c r="J62" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K62" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
         <v>1.94</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -12591,22 +12591,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G63" t="n">
         <v>1.82</v>
       </c>
       <c r="H63" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J63" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K63" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -12621,7 +12621,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q63" t="n">
         <v>1.6</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -12979,22 +12979,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G65" t="n">
         <v>5.5</v>
       </c>
       <c r="H65" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="I65" t="n">
         <v>2.9</v>
       </c>
       <c r="J65" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="K65" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -13009,7 +13009,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q65" t="n">
         <v>2.84</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -13173,22 +13173,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
         <v>4.6</v>
       </c>
       <c r="H66" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I66" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K66" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -13203,7 +13203,7 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="Q66" t="n">
         <v>2.12</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
         <v>3.55</v>
       </c>
       <c r="K67" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L67" t="n">
         <v>1.01</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -13570,7 +13570,7 @@
         <v>1.95</v>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J68" t="n">
         <v>3.7</v>
@@ -13594,7 +13594,7 @@
         <v>2.08</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -13755,16 +13755,16 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G69" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="H69" t="n">
         <v>1.42</v>
       </c>
       <c r="I69" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>5</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -13949,22 +13949,22 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="G70" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="H70" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I70" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J70" t="n">
         <v>2.84</v>
       </c>
-      <c r="I70" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J70" t="n">
-        <v>2.72</v>
-      </c>
       <c r="K70" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -13979,7 +13979,7 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Q70" t="n">
         <v>3.05</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -14149,10 +14149,10 @@
         <v>2.28</v>
       </c>
       <c r="H71" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I71" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J71" t="n">
         <v>3.9</v>
@@ -14197,7 +14197,7 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y71" t="n">
         <v>19.5</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -14340,10 +14340,10 @@
         <v>1.66</v>
       </c>
       <c r="G72" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H72" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I72" t="n">
         <v>6.2</v>
@@ -14445,7 +14445,7 @@
         <v>130</v>
       </c>
       <c r="AP72" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ72" t="n">
         <v>16</v>
@@ -14466,7 +14466,7 @@
         <v>19.5</v>
       </c>
       <c r="AW72" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AX72" t="n">
         <v>8.6</v>
@@ -14487,7 +14487,7 @@
         <v>15.5</v>
       </c>
       <c r="BD72" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE72" t="n">
         <v>42</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="G74" t="n">
         <v>3</v>
@@ -14734,10 +14734,10 @@
         <v>1.5</v>
       </c>
       <c r="I74" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="J74" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="K74" t="n">
         <v>5.6</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -14931,7 +14931,7 @@
         <v>1000</v>
       </c>
       <c r="J75" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K75" t="n">
         <v>1000</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -16083,7 +16083,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="G81" t="n">
         <v>1.63</v>
@@ -16095,10 +16095,10 @@
         <v>1000</v>
       </c>
       <c r="J81" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="K81" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -16277,22 +16277,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G82" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H82" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I82" t="n">
         <v>4.6</v>
       </c>
       <c r="J82" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K82" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -16301,16 +16301,16 @@
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="O82" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P82" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -16471,22 +16471,22 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G83" t="n">
         <v>2.98</v>
       </c>
       <c r="H83" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I83" t="n">
         <v>4.7</v>
       </c>
       <c r="J83" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="K83" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16698,7 @@
         <v>1.25</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -16859,22 +16859,22 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G85" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H85" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I85" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K85" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -16889,10 +16889,10 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="G88" t="n">
         <v>1.74</v>
@@ -17450,13 +17450,13 @@
         <v>5.5</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K88" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -17471,10 +17471,10 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q88" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -17647,7 +17647,7 @@
         <v>2.46</v>
       </c>
       <c r="J89" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="K89" t="n">
         <v>3.85</v>
@@ -17665,10 +17665,10 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -17829,22 +17829,22 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G90" t="n">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="H90" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="I90" t="n">
         <v>5.2</v>
       </c>
       <c r="J90" t="n">
-        <v>1.23</v>
+        <v>2.48</v>
       </c>
       <c r="K90" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -17862,7 +17862,7 @@
         <v>1.25</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -18026,16 +18026,16 @@
         <v>2.88</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="H91" t="n">
         <v>2.66</v>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="K91" t="n">
         <v>3.65</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -18220,16 +18220,16 @@
         <v>2.08</v>
       </c>
       <c r="G92" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H92" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="I92" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="J92" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K92" t="n">
         <v>3.75</v>
@@ -18247,10 +18247,10 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -18605,22 +18605,22 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G94" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="H94" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I94" t="n">
         <v>4.5</v>
       </c>
       <c r="J94" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K94" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -18635,7 +18635,7 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q94" t="n">
         <v>2.18</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -18808,7 +18808,7 @@
         <v>1.09</v>
       </c>
       <c r="I95" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J95" t="n">
         <v>4.5</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -19193,7 +19193,7 @@
         <v>3</v>
       </c>
       <c r="H97" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I97" t="n">
         <v>4.2</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-03 02:35:52</t>
+          <t>2026-04-03 05:07:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-05.xlsx
@@ -763,10 +763,10 @@
         <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="I2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="J2" t="n">
         <v>4.2</v>
@@ -796,16 +796,16 @@
         <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
         <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="W2" t="n">
         <v>1.22</v>
@@ -820,19 +820,19 @@
         <v>11.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AB2" t="n">
         <v>22</v>
       </c>
       <c r="AC2" t="n">
-        <v>40</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
         <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AF2" t="n">
         <v>50</v>
@@ -841,7 +841,7 @@
         <v>21</v>
       </c>
       <c r="AH2" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI2" t="n">
         <v>36</v>
@@ -874,7 +874,7 @@
         <v>10</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
         <v>7.8</v>
@@ -901,10 +901,10 @@
         <v>9</v>
       </c>
       <c r="BB2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G3" t="n">
         <v>1.59</v>
@@ -966,7 +966,7 @@
         <v>4.9</v>
       </c>
       <c r="K3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -990,10 +990,10 @@
         <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U3" t="n">
         <v>2.42</v>
@@ -1023,10 +1023,10 @@
         <v>12.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
         <v>12.5</v>
@@ -1035,13 +1035,13 @@
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
         <v>15.5</v>
@@ -1065,10 +1065,10 @@
         <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT3" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
         <v>17.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1089,13 +1089,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC3" t="n">
         <v>13.5</v>
@@ -1104,17 +1104,17 @@
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3" t="n">
         <v>4.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
         <v>2.76</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
         <v>1.65</v>
@@ -1253,52 +1253,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -1447,52 +1447,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>2.48</v>
       </c>
       <c r="G7" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H7" t="n">
         <v>3.15</v>
       </c>
       <c r="I7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J7" t="n">
         <v>2.82</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1790,7 +1790,7 @@
         <v>27</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
         <v>11.5</v>
@@ -1805,7 +1805,7 @@
         <v>48</v>
       </c>
       <c r="AF7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG7" t="n">
         <v>13.5</v>
@@ -1814,10 +1814,10 @@
         <v>18.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK7" t="n">
         <v>32</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO7" t="n">
         <v>48</v>
@@ -1850,7 +1850,7 @@
         <v>8.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
         <v>12.5</v>
@@ -1880,7 +1880,7 @@
         <v>30</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7" t="n">
         <v>16.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>3.55</v>
       </c>
       <c r="I8" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J8" t="n">
         <v>3.95</v>
@@ -1939,7 +1939,7 @@
         <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
@@ -1966,10 +1966,10 @@
         <v>1.57</v>
       </c>
       <c r="U8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
         <v>1.89</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
         <v>1.96</v>
@@ -2154,7 +2154,7 @@
         <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
         <v>1.79</v>
@@ -2193,7 +2193,7 @@
         <v>50</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG9" t="n">
         <v>11.5</v>
@@ -2232,7 +2232,7 @@
         <v>6.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT9" t="n">
         <v>8.4</v>
@@ -2268,17 +2268,17 @@
         <v>30</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
         <v>14</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="G10" t="n">
         <v>2.16</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
@@ -2324,7 +2324,7 @@
         <v>3.15</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2360,13 +2360,13 @@
         <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X10" t="n">
         <v>11.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
         <v>34</v>
@@ -2375,19 +2375,19 @@
         <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC10" t="n">
         <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE10" t="n">
         <v>70</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2414,7 +2414,7 @@
         <v>21</v>
       </c>
       <c r="AO10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="n">
         <v>9.6</v>
@@ -2423,10 +2423,10 @@
         <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT10" t="n">
         <v>6.8</v>
@@ -2438,7 +2438,7 @@
         <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
         <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB10" t="n">
         <v>21</v>
@@ -2462,17 +2462,17 @@
         <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF10" t="n">
         <v>15</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -2536,13 +2536,13 @@
         <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R11" t="n">
         <v>1.61</v>
       </c>
       <c r="S11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
         <v>1.6</v>
@@ -2560,10 +2560,10 @@
         <v>24</v>
       </c>
       <c r="Y11" t="n">
-        <v>140</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AA11" t="n">
         <v>22</v>
@@ -2578,22 +2578,22 @@
         <v>11</v>
       </c>
       <c r="AE11" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AF11" t="n">
         <v>34</v>
       </c>
       <c r="AG11" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI11" t="n">
         <v>27</v>
       </c>
       <c r="AJ11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK11" t="n">
         <v>42</v>
@@ -2623,7 +2623,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
         <v>9</v>
@@ -2632,7 +2632,7 @@
         <v>9.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX11" t="n">
         <v>9.6</v>
@@ -2644,7 +2644,7 @@
         <v>14</v>
       </c>
       <c r="BA11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB11" t="n">
         <v>11</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
         <v>3.85</v>
@@ -2721,16 +2721,16 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R12" t="n">
         <v>1.46</v>
@@ -2739,13 +2739,13 @@
         <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U12" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
         <v>1.98</v>
@@ -2775,7 +2775,7 @@
         <v>55</v>
       </c>
       <c r="AF12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
         <v>11</v>
@@ -2814,7 +2814,7 @@
         <v>23</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT12" t="n">
         <v>9.6</v>
@@ -2826,7 +2826,7 @@
         <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX12" t="n">
         <v>11.5</v>
@@ -2838,7 +2838,7 @@
         <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB12" t="n">
         <v>19.5</v>
@@ -2850,17 +2850,17 @@
         <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
         <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
         <v>3.3</v>
@@ -2912,28 +2912,28 @@
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U13" t="n">
         <v>2.46</v>
@@ -2942,13 +2942,13 @@
         <v>1.43</v>
       </c>
       <c r="W13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
       </c>
       <c r="Y13" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
         <v>26</v>
@@ -2960,7 +2960,7 @@
         <v>14</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD13" t="n">
         <v>15</v>
@@ -3002,16 +3002,16 @@
         <v>17.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
         <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU13" t="n">
         <v>8.199999999999999</v>
@@ -3029,32 +3029,32 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC13" t="n">
         <v>16.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
         <v>44</v>
       </c>
       <c r="BF13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG13" t="n">
         <v>19</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -3088,13 +3088,13 @@
         <v>1.53</v>
       </c>
       <c r="G14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H14" t="n">
         <v>6.6</v>
       </c>
       <c r="I14" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
         <v>4.6</v>
@@ -3115,28 +3115,28 @@
         <v>1.21</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q14" t="n">
         <v>1.62</v>
       </c>
       <c r="R14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T14" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
         <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X14" t="n">
         <v>28</v>
@@ -3160,7 +3160,7 @@
         <v>27</v>
       </c>
       <c r="AE14" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF14" t="n">
         <v>10.5</v>
@@ -3190,7 +3190,7 @@
         <v>6.4</v>
       </c>
       <c r="AO14" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AP14" t="n">
         <v>20</v>
@@ -3199,7 +3199,7 @@
         <v>20</v>
       </c>
       <c r="AR14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS14" t="n">
         <v>10</v>
@@ -3211,10 +3211,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX14" t="n">
         <v>9</v>
@@ -3223,10 +3223,10 @@
         <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB14" t="n">
         <v>12.5</v>
@@ -3235,10 +3235,10 @@
         <v>13</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF14" t="n">
         <v>5.7</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>3.85</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H15" t="n">
         <v>1.63</v>
@@ -3303,25 +3303,25 @@
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="O15" t="n">
         <v>1.16</v>
       </c>
       <c r="P15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R15" t="n">
         <v>1.57</v>
       </c>
       <c r="S15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="U15" t="n">
         <v>1.01</v>
@@ -3330,7 +3330,7 @@
         <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
         <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
         <v>1.12</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G18" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H18" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J18" t="n">
         <v>3.75</v>
@@ -3888,7 +3888,7 @@
         <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P18" t="n">
         <v>2.12</v>
@@ -3900,19 +3900,19 @@
         <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U18" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V18" t="n">
         <v>1.53</v>
       </c>
       <c r="W18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X18" t="n">
         <v>21</v>
@@ -3978,7 +3978,7 @@
         <v>16.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT18" t="n">
         <v>10.5</v>
@@ -4002,16 +4002,16 @@
         <v>13.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC18" t="n">
         <v>19</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE18" t="n">
         <v>4.7</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -4115,13 +4115,13 @@
         <v>9</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA19" t="n">
         <v>19.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC19" t="n">
         <v>9.4</v>
@@ -4133,7 +4133,7 @@
         <v>19.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AG19" t="n">
         <v>22</v>
@@ -4148,10 +4148,10 @@
         <v>160</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="n">
         <v>130</v>
@@ -4187,7 +4187,7 @@
         <v>15.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="AY19" t="n">
         <v>17.5</v>
@@ -4196,29 +4196,29 @@
         <v>17.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
         <v>2.14</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="V22" t="n">
         <v>1.09</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G24" t="n">
         <v>2.3</v>
@@ -5040,7 +5040,7 @@
         <v>2.94</v>
       </c>
       <c r="K24" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L24" t="n">
         <v>1.36</v>
@@ -5049,16 +5049,16 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="O24" t="n">
         <v>1.28</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="R24" t="n">
         <v>1.3</v>
@@ -5070,7 +5070,7 @@
         <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V24" t="n">
         <v>1.31</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
         <v>1.62</v>
       </c>
       <c r="I25" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>4.1</v>
@@ -5237,7 +5237,7 @@
         <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
@@ -5255,7 +5255,7 @@
         <v>1.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S25" t="n">
         <v>2.84</v>
@@ -5267,7 +5267,7 @@
         <v>2.08</v>
       </c>
       <c r="V25" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="W25" t="n">
         <v>1.18</v>
@@ -5285,7 +5285,7 @@
         <v>18</v>
       </c>
       <c r="AB25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC25" t="n">
         <v>10.5</v>
@@ -5297,7 +5297,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG25" t="n">
         <v>23</v>
@@ -5360,29 +5360,29 @@
         <v>16.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE25" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE25" t="n">
+      <c r="BF25" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>7.4</v>
       </c>
       <c r="BG25" t="n">
         <v>7.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G26" t="n">
         <v>1.54</v>
@@ -5425,7 +5425,7 @@
         <v>6.6</v>
       </c>
       <c r="J26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K26" t="n">
         <v>5.6</v>
@@ -5440,28 +5440,28 @@
         <v>6.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P26" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q26" t="n">
         <v>1.47</v>
       </c>
       <c r="R26" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S26" t="n">
         <v>2.16</v>
       </c>
       <c r="T26" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U26" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W26" t="n">
         <v>2.84</v>
@@ -5491,7 +5491,7 @@
         <v>70</v>
       </c>
       <c r="AF26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG26" t="n">
         <v>11</v>
@@ -5521,40 +5521,40 @@
         <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR26" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS26" t="n">
         <v>10</v>
       </c>
       <c r="AT26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU26" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV26" t="n">
         <v>20</v>
       </c>
       <c r="AW26" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX26" t="n">
         <v>10.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ26" t="n">
         <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB26" t="n">
         <v>13</v>
@@ -5566,17 +5566,17 @@
         <v>20</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -5610,10 +5610,10 @@
         <v>6.6</v>
       </c>
       <c r="G27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H27" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I27" t="n">
         <v>1.51</v>
@@ -5634,13 +5634,13 @@
         <v>6.6</v>
       </c>
       <c r="O27" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P27" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R27" t="n">
         <v>1.79</v>
@@ -5649,16 +5649,16 @@
         <v>2.12</v>
       </c>
       <c r="T27" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U27" t="n">
         <v>2.34</v>
       </c>
       <c r="V27" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="W27" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
         <v>34</v>
@@ -5709,7 +5709,7 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
         <v>4.9</v>
@@ -5721,7 +5721,7 @@
         <v>11.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS27" t="n">
         <v>12</v>
@@ -5733,7 +5733,7 @@
         <v>11</v>
       </c>
       <c r="AV27" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW27" t="n">
         <v>12</v>
@@ -5766,11 +5766,11 @@
         <v>6.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G28" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H28" t="n">
         <v>2.22</v>
@@ -5813,10 +5813,10 @@
         <v>2.24</v>
       </c>
       <c r="J28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.55</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.6</v>
       </c>
       <c r="L28" t="n">
         <v>1.45</v>
@@ -5852,7 +5852,7 @@
         <v>1.81</v>
       </c>
       <c r="W28" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X28" t="n">
         <v>12.5</v>
@@ -5867,7 +5867,7 @@
         <v>28</v>
       </c>
       <c r="AB28" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC28" t="n">
         <v>7.8</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -5995,19 +5995,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H29" t="n">
         <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K29" t="n">
         <v>4.4</v>
@@ -6016,37 +6016,37 @@
         <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N29" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S29" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="U29" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="V29" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W29" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X29" t="n">
         <v>19</v>
@@ -6055,10 +6055,10 @@
         <v>18.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA29" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB29" t="n">
         <v>11</v>
@@ -6067,10 +6067,10 @@
         <v>11</v>
       </c>
       <c r="AD29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE29" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF29" t="n">
         <v>14</v>
@@ -6079,10 +6079,10 @@
         <v>12.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI29" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ29" t="n">
         <v>25</v>
@@ -6094,13 +6094,13 @@
         <v>44</v>
       </c>
       <c r="AM29" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN29" t="n">
         <v>15</v>
       </c>
       <c r="AO29" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP29" t="n">
         <v>11.5</v>
@@ -6115,7 +6115,7 @@
         <v>70</v>
       </c>
       <c r="AT29" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU29" t="n">
         <v>6.8</v>
@@ -6127,7 +6127,7 @@
         <v>40</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY29" t="n">
         <v>7.8</v>
@@ -6151,14 +6151,14 @@
         <v>70</v>
       </c>
       <c r="BF29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG29" t="n">
         <v>44</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
         <v>3.75</v>
       </c>
       <c r="L30" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
         <v>1.09</v>
@@ -6216,16 +6216,16 @@
         <v>3.3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P30" t="n">
         <v>1.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
         <v>4.2</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         <v>1.7</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K31" t="n">
         <v>4.7</v>
@@ -6416,13 +6416,13 @@
         <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R31" t="n">
         <v>1.43</v>
       </c>
       <c r="S31" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T31" t="n">
         <v>1.81</v>
@@ -6482,7 +6482,7 @@
         <v>80</v>
       </c>
       <c r="AM31" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN31" t="n">
         <v>110</v>
@@ -6530,7 +6530,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BC31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD31" t="n">
         <v>8.199999999999999</v>
@@ -6539,14 +6539,14 @@
         <v>8.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG31" t="n">
         <v>6.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
         <v>6.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV32" t="n">
         <v>16</v>
@@ -6718,7 +6718,7 @@
         <v>22</v>
       </c>
       <c r="BA32" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BB32" t="n">
         <v>25</v>
@@ -6727,7 +6727,7 @@
         <v>26</v>
       </c>
       <c r="BD32" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BE32" t="n">
         <v>48</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
         <v>15.5</v>
       </c>
       <c r="H35" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="I35" t="n">
         <v>1.46</v>
@@ -7183,7 +7183,7 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O35" t="n">
         <v>1.38</v>
@@ -7192,7 +7192,7 @@
         <v>1.65</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="R35" t="n">
         <v>1.24</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7395,7 @@
         <v>2.84</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U36" t="n">
         <v>1.01</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -7741,16 +7741,16 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="G38" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="H38" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J38" t="n">
         <v>3.2</v>
@@ -7759,25 +7759,25 @@
         <v>3.6</v>
       </c>
       <c r="L38" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M38" t="n">
         <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O38" t="n">
         <v>1.37</v>
       </c>
       <c r="P38" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q38" t="n">
         <v>2.08</v>
       </c>
       <c r="R38" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
         <v>3.75</v>
@@ -7789,10 +7789,10 @@
         <v>2.02</v>
       </c>
       <c r="V38" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W38" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X38" t="n">
         <v>15</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="AA38" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AB38" t="n">
         <v>11</v>
@@ -7819,31 +7819,31 @@
         <v>50</v>
       </c>
       <c r="AF38" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG38" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH38" t="n">
         <v>21</v>
       </c>
       <c r="AI38" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ38" t="n">
         <v>38</v>
       </c>
       <c r="AK38" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL38" t="n">
         <v>55</v>
       </c>
       <c r="AM38" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN38" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO38" t="n">
         <v>55</v>
@@ -7858,7 +7858,7 @@
         <v>16</v>
       </c>
       <c r="AS38" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT38" t="n">
         <v>8.199999999999999</v>
@@ -7870,7 +7870,7 @@
         <v>12</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX38" t="n">
         <v>11.5</v>
@@ -7885,26 +7885,26 @@
         <v>4.5</v>
       </c>
       <c r="BB38" t="n">
-        <v>25</v>
+        <v>4.4</v>
       </c>
       <c r="BC38" t="n">
         <v>21</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF38" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BG38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>2.48</v>
       </c>
       <c r="G39" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H39" t="n">
         <v>3.2</v>
@@ -7953,7 +7953,7 @@
         <v>3.3</v>
       </c>
       <c r="L39" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M39" t="n">
         <v>1.11</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G40" t="n">
         <v>2.28</v>
@@ -8171,7 +8171,7 @@
         <v>2.12</v>
       </c>
       <c r="T40" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="U40" t="n">
         <v>1.01</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -8326,16 +8326,16 @@
         <v>1.82</v>
       </c>
       <c r="G41" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="H41" t="n">
         <v>4.3</v>
       </c>
       <c r="I41" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J41" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K41" t="n">
         <v>4.2</v>
@@ -8344,7 +8344,7 @@
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N41" t="n">
         <v>3.45</v>
@@ -8359,7 +8359,7 @@
         <v>2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S41" t="n">
         <v>3.55</v>
@@ -8368,16 +8368,16 @@
         <v>1.89</v>
       </c>
       <c r="U41" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V41" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W41" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X41" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y41" t="n">
         <v>18.5</v>
@@ -8392,7 +8392,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC41" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD41" t="n">
         <v>23</v>
@@ -8404,10 +8404,10 @@
         <v>13.5</v>
       </c>
       <c r="AG41" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI41" t="n">
         <v>1000</v>
@@ -8416,7 +8416,7 @@
         <v>26</v>
       </c>
       <c r="AK41" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL41" t="n">
         <v>48</v>
@@ -8431,49 +8431,49 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ41" t="n">
         <v>11</v>
       </c>
       <c r="AR41" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT41" t="n">
         <v>7.2</v>
       </c>
       <c r="AU41" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV41" t="n">
         <v>13.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX41" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY41" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ41" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB41" t="n">
         <v>18</v>
       </c>
       <c r="BC41" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE41" t="n">
         <v>4.2</v>
@@ -8482,11 +8482,11 @@
         <v>10.5</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G42" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="H42" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I42" t="n">
         <v>5</v>
       </c>
       <c r="J42" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K42" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -8541,19 +8541,19 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>2.18</v>
+        <v>3.5</v>
       </c>
       <c r="O42" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P42" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q42" t="n">
         <v>1.48</v>
       </c>
       <c r="R42" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S42" t="n">
         <v>2.18</v>
@@ -8568,7 +8568,7 @@
         <v>1.25</v>
       </c>
       <c r="W42" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -8714,13 +8714,13 @@
         <v>2.56</v>
       </c>
       <c r="G43" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H43" t="n">
         <v>2.84</v>
       </c>
       <c r="I43" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J43" t="n">
         <v>3.5</v>
@@ -8741,28 +8741,28 @@
         <v>1.29</v>
       </c>
       <c r="P43" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q43" t="n">
         <v>1.87</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S43" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T43" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U43" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V43" t="n">
         <v>1.5</v>
       </c>
       <c r="W43" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X43" t="n">
         <v>18</v>
@@ -8780,13 +8780,13 @@
         <v>12.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD43" t="n">
         <v>15</v>
       </c>
       <c r="AE43" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF43" t="n">
         <v>21</v>
@@ -8810,7 +8810,7 @@
         <v>40</v>
       </c>
       <c r="AM43" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN43" t="n">
         <v>22</v>
@@ -8822,19 +8822,19 @@
         <v>14</v>
       </c>
       <c r="AQ43" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR43" t="n">
         <v>17.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT43" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU43" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV43" t="n">
         <v>11</v>
@@ -8846,25 +8846,25 @@
         <v>15</v>
       </c>
       <c r="AY43" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ43" t="n">
         <v>13.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB43" t="n">
         <v>30</v>
       </c>
       <c r="BC43" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD43" t="n">
         <v>30</v>
       </c>
       <c r="BE43" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF43" t="n">
         <v>16</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -8947,10 +8947,10 @@
         <v>3.1</v>
       </c>
       <c r="T44" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="U44" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="V44" t="n">
         <v>1.1</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -9293,28 +9293,28 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="G46" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="H46" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J46" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K46" t="n">
         <v>3.65</v>
       </c>
       <c r="L46" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M46" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N46" t="n">
         <v>3</v>
@@ -9323,13 +9323,13 @@
         <v>1.31</v>
       </c>
       <c r="P46" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="R46" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S46" t="n">
         <v>3.4</v>
@@ -9341,10 +9341,10 @@
         <v>2.12</v>
       </c>
       <c r="V46" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W46" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X46" t="n">
         <v>17</v>
@@ -9371,7 +9371,7 @@
         <v>42</v>
       </c>
       <c r="AF46" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG46" t="n">
         <v>14.5</v>
@@ -9383,22 +9383,22 @@
         <v>55</v>
       </c>
       <c r="AJ46" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK46" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL46" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM46" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN46" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AO46" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP46" t="n">
         <v>11.5</v>
@@ -9410,7 +9410,7 @@
         <v>17</v>
       </c>
       <c r="AS46" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT46" t="n">
         <v>9.199999999999999</v>
@@ -9422,7 +9422,7 @@
         <v>11</v>
       </c>
       <c r="AW46" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AX46" t="n">
         <v>14.5</v>
@@ -9434,29 +9434,29 @@
         <v>14.5</v>
       </c>
       <c r="BA46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC46" t="n">
         <v>4</v>
       </c>
-      <c r="BB46" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BD46" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE46" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF46" t="n">
         <v>17.5</v>
       </c>
       <c r="BG46" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
         <v>18.5</v>
       </c>
       <c r="AK47" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL47" t="n">
         <v>85</v>
@@ -9589,13 +9589,13 @@
         <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO47" t="n">
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AQ47" t="n">
         <v>4.3</v>
@@ -9604,53 +9604,53 @@
         <v>5.1</v>
       </c>
       <c r="AS47" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT47" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU47" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AV47" t="n">
         <v>4.8</v>
       </c>
       <c r="AW47" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX47" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AY47" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AZ47" t="n">
         <v>4.8</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB47" t="n">
         <v>4.2</v>
       </c>
       <c r="BC47" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD47" t="n">
         <v>5.1</v>
       </c>
       <c r="BE47" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF47" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="BG47" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -9687,13 +9687,13 @@
         <v>6.4</v>
       </c>
       <c r="H48" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I48" t="n">
         <v>1.75</v>
       </c>
       <c r="J48" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K48" t="n">
         <v>4.7</v>
@@ -9711,7 +9711,7 @@
         <v>1.22</v>
       </c>
       <c r="P48" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q48" t="n">
         <v>1.62</v>
@@ -9747,7 +9747,7 @@
         <v>23</v>
       </c>
       <c r="AB48" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC48" t="n">
         <v>12</v>
@@ -9768,13 +9768,13 @@
         <v>22</v>
       </c>
       <c r="AI48" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ48" t="n">
         <v>140</v>
       </c>
       <c r="AK48" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL48" t="n">
         <v>70</v>
@@ -9786,13 +9786,13 @@
         <v>70</v>
       </c>
       <c r="AO48" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP48" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR48" t="n">
         <v>8.800000000000001</v>
@@ -9813,7 +9813,7 @@
         <v>12.5</v>
       </c>
       <c r="AX48" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AY48" t="n">
         <v>14</v>
@@ -9834,17 +9834,17 @@
         <v>4</v>
       </c>
       <c r="BE48" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF48" t="n">
         <v>4</v>
       </c>
       <c r="BG48" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G49" t="n">
         <v>2.68</v>
@@ -9890,7 +9890,7 @@
         <v>3.2</v>
       </c>
       <c r="K49" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L49" t="n">
         <v>1.52</v>
@@ -9899,16 +9899,16 @@
         <v>1.11</v>
       </c>
       <c r="N49" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
         <v>1.47</v>
       </c>
       <c r="P49" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R49" t="n">
         <v>1.25</v>
@@ -9920,7 +9920,7 @@
         <v>2.02</v>
       </c>
       <c r="U49" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V49" t="n">
         <v>1.45</v>
@@ -9950,7 +9950,7 @@
         <v>14</v>
       </c>
       <c r="AE49" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AF49" t="n">
         <v>15</v>
@@ -9962,7 +9962,7 @@
         <v>20</v>
       </c>
       <c r="AI49" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ49" t="n">
         <v>40</v>
@@ -9992,7 +9992,7 @@
         <v>18</v>
       </c>
       <c r="AS49" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AT49" t="n">
         <v>8.199999999999999</v>
@@ -10010,7 +10010,7 @@
         <v>14.5</v>
       </c>
       <c r="AY49" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ49" t="n">
         <v>19</v>
@@ -10019,7 +10019,7 @@
         <v>50</v>
       </c>
       <c r="BB49" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC49" t="n">
         <v>30</v>
@@ -10028,17 +10028,17 @@
         <v>46</v>
       </c>
       <c r="BE49" t="n">
-        <v>19.5</v>
+        <v>44</v>
       </c>
       <c r="BF49" t="n">
         <v>29</v>
       </c>
       <c r="BG49" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -10108,10 +10108,10 @@
         <v>1.28</v>
       </c>
       <c r="S50" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T50" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U50" t="n">
         <v>2.02</v>
@@ -10177,7 +10177,7 @@
         <v>32</v>
       </c>
       <c r="AP50" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ50" t="n">
         <v>9</v>
@@ -10186,7 +10186,7 @@
         <v>15</v>
       </c>
       <c r="AS50" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AT50" t="n">
         <v>9.6</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -10296,22 +10296,22 @@
         <v>1.79</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R51" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
       </c>
       <c r="T51" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U51" t="n">
         <v>2.04</v>
       </c>
       <c r="V51" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W51" t="n">
         <v>1.72</v>
@@ -10416,17 +10416,17 @@
         <v>38</v>
       </c>
       <c r="BE51" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="BF51" t="n">
         <v>20</v>
       </c>
       <c r="BG51" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G52" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H52" t="n">
         <v>6</v>
@@ -10481,7 +10481,7 @@
         <v>1.03</v>
       </c>
       <c r="N52" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O52" t="n">
         <v>1.19</v>
@@ -10502,13 +10502,13 @@
         <v>1.59</v>
       </c>
       <c r="U52" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V52" t="n">
         <v>1.16</v>
       </c>
       <c r="W52" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X52" t="n">
         <v>32</v>
@@ -10526,7 +10526,7 @@
         <v>12</v>
       </c>
       <c r="AC52" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD52" t="n">
         <v>26</v>
@@ -10568,13 +10568,13 @@
         <v>21</v>
       </c>
       <c r="AQ52" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR52" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AS52" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AT52" t="n">
         <v>9.6</v>
@@ -10586,7 +10586,7 @@
         <v>20</v>
       </c>
       <c r="AW52" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX52" t="n">
         <v>9.4</v>
@@ -10598,7 +10598,7 @@
         <v>16.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB52" t="n">
         <v>13</v>
@@ -10607,20 +10607,20 @@
         <v>12.5</v>
       </c>
       <c r="BD52" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE52" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF52" t="n">
         <v>5.3</v>
       </c>
       <c r="BG52" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -10726,7 +10726,7 @@
         <v>15</v>
       </c>
       <c r="AE53" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF53" t="n">
         <v>14.5</v>
@@ -10738,7 +10738,7 @@
         <v>16</v>
       </c>
       <c r="AI53" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ53" t="n">
         <v>26</v>
@@ -10768,7 +10768,7 @@
         <v>25</v>
       </c>
       <c r="AS53" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AT53" t="n">
         <v>11</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -11039,16 +11039,16 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="G55" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H55" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="I55" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="J55" t="n">
         <v>4</v>
@@ -11063,7 +11063,7 @@
         <v>1.04</v>
       </c>
       <c r="N55" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O55" t="n">
         <v>1.21</v>
@@ -11072,7 +11072,7 @@
         <v>2.32</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R55" t="n">
         <v>1.52</v>
@@ -11087,10 +11087,10 @@
         <v>2.34</v>
       </c>
       <c r="V55" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="W55" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X55" t="n">
         <v>23</v>
@@ -11141,7 +11141,7 @@
         <v>70</v>
       </c>
       <c r="AN55" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO55" t="n">
         <v>10.5</v>
@@ -11183,7 +11183,7 @@
         <v>6.8</v>
       </c>
       <c r="BB55" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BC55" t="n">
         <v>7.4</v>
@@ -11192,7 +11192,7 @@
         <v>7.4</v>
       </c>
       <c r="BE55" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF55" t="n">
         <v>7</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -11236,10 +11236,10 @@
         <v>2.46</v>
       </c>
       <c r="G56" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H56" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I56" t="n">
         <v>3.55</v>
@@ -11248,7 +11248,7 @@
         <v>3.05</v>
       </c>
       <c r="K56" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
@@ -11284,7 +11284,7 @@
         <v>1.39</v>
       </c>
       <c r="W56" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X56" t="n">
         <v>1000</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -11436,10 +11436,10 @@
         <v>6.4</v>
       </c>
       <c r="I57" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J57" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K57" t="n">
         <v>5.5</v>
@@ -11451,34 +11451,34 @@
         <v>1.03</v>
       </c>
       <c r="N57" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O57" t="n">
         <v>1.16</v>
       </c>
       <c r="P57" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R57" t="n">
         <v>1.75</v>
       </c>
       <c r="S57" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T57" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U57" t="n">
         <v>2.38</v>
       </c>
       <c r="V57" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W57" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X57" t="n">
         <v>38</v>
@@ -11487,7 +11487,7 @@
         <v>36</v>
       </c>
       <c r="Z57" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA57" t="n">
         <v>200</v>
@@ -11520,7 +11520,7 @@
         <v>16</v>
       </c>
       <c r="AK57" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL57" t="n">
         <v>27</v>
@@ -11538,10 +11538,10 @@
         <v>6.2</v>
       </c>
       <c r="AQ57" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR57" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS57" t="n">
         <v>7.4</v>
@@ -11568,7 +11568,7 @@
         <v>16</v>
       </c>
       <c r="BA57" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB57" t="n">
         <v>12.5</v>
@@ -11580,7 +11580,7 @@
         <v>21</v>
       </c>
       <c r="BE57" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF57" t="n">
         <v>4</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -11624,19 +11624,19 @@
         <v>1.72</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H58" t="n">
         <v>5.6</v>
       </c>
       <c r="I58" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J58" t="n">
         <v>3.55</v>
       </c>
       <c r="K58" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -11648,7 +11648,7 @@
         <v>2.66</v>
       </c>
       <c r="O58" t="n">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="P58" t="n">
         <v>1.72</v>
@@ -11672,7 +11672,7 @@
         <v>1.17</v>
       </c>
       <c r="W58" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X58" t="n">
         <v>14.5</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
         <v>3.35</v>
       </c>
       <c r="H59" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I59" t="n">
         <v>2.66</v>
@@ -11833,7 +11833,7 @@
         <v>3.15</v>
       </c>
       <c r="L59" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M59" t="n">
         <v>1.11</v>
@@ -11845,7 +11845,7 @@
         <v>1.46</v>
       </c>
       <c r="P59" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q59" t="n">
         <v>2.42</v>
@@ -11857,10 +11857,10 @@
         <v>4.7</v>
       </c>
       <c r="T59" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U59" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V59" t="n">
         <v>1.6</v>
@@ -11932,7 +11932,7 @@
         <v>14.5</v>
       </c>
       <c r="AS59" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT59" t="n">
         <v>9.6</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -12012,7 +12012,7 @@
         <v>1.47</v>
       </c>
       <c r="G60" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="H60" t="n">
         <v>4.7</v>
@@ -12021,7 +12021,7 @@
         <v>12</v>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K60" t="n">
         <v>1000</v>
@@ -12060,7 +12060,7 @@
         <v>1.11</v>
       </c>
       <c r="W60" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -12203,22 +12203,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G61" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="H61" t="n">
         <v>7.8</v>
       </c>
       <c r="I61" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J61" t="n">
         <v>5.4</v>
       </c>
       <c r="K61" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -12230,55 +12230,55 @@
         <v>6</v>
       </c>
       <c r="O61" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P61" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R61" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S61" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T61" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U61" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="V61" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W61" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="X61" t="n">
         <v>36</v>
       </c>
       <c r="Y61" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z61" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AA61" t="n">
         <v>1000</v>
       </c>
       <c r="AB61" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC61" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD61" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE61" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF61" t="n">
         <v>12</v>
@@ -12287,10 +12287,10 @@
         <v>12.5</v>
       </c>
       <c r="AH61" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI61" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ61" t="n">
         <v>14</v>
@@ -12305,22 +12305,22 @@
         <v>120</v>
       </c>
       <c r="AN61" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AO61" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AP61" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ61" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AR61" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS61" t="n">
         <v>5.5</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>5.7</v>
       </c>
       <c r="AT61" t="n">
         <v>9.199999999999999</v>
@@ -12329,44 +12329,44 @@
         <v>10.5</v>
       </c>
       <c r="AV61" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AW61" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AX61" t="n">
         <v>8</v>
       </c>
       <c r="AY61" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AZ61" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BA61" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BB61" t="n">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="BC61" t="n">
         <v>10.5</v>
       </c>
       <c r="BD61" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BE61" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BF61" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BG61" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13582,7 @@
         <v>1.01</v>
       </c>
       <c r="M68" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N68" t="n">
         <v>2.42</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -13761,16 +13761,16 @@
         <v>1000</v>
       </c>
       <c r="H69" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="I69" t="n">
         <v>5</v>
       </c>
       <c r="J69" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="K69" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L69" t="n">
         <v>1.01</v>
@@ -13863,52 +13863,52 @@
         <v>1000</v>
       </c>
       <c r="AP69" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ69" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR69" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS69" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT69" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU69" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV69" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW69" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX69" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY69" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ69" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA69" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB69" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC69" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD69" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE69" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF69" t="n">
         <v>1.01</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -13949,7 +13949,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G70" t="n">
         <v>1.64</v>
@@ -13979,7 +13979,7 @@
         <v>1.29</v>
       </c>
       <c r="P70" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q70" t="n">
         <v>1.88</v>
@@ -13994,13 +13994,13 @@
         <v>1.95</v>
       </c>
       <c r="U70" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V70" t="n">
         <v>1.14</v>
       </c>
       <c r="W70" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X70" t="n">
         <v>17.5</v>
@@ -14012,7 +14012,7 @@
         <v>65</v>
       </c>
       <c r="AA70" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AB70" t="n">
         <v>8.199999999999999</v>
@@ -14024,10 +14024,10 @@
         <v>29</v>
       </c>
       <c r="AE70" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF70" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG70" t="n">
         <v>10.5</v>
@@ -14048,13 +14048,13 @@
         <v>38</v>
       </c>
       <c r="AM70" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN70" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AO70" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP70" t="n">
         <v>13.5</v>
@@ -14063,10 +14063,10 @@
         <v>20</v>
       </c>
       <c r="AR70" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS70" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT70" t="n">
         <v>7.2</v>
@@ -14075,10 +14075,10 @@
         <v>8.4</v>
       </c>
       <c r="AV70" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW70" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX70" t="n">
         <v>8.199999999999999</v>
@@ -14090,7 +14090,7 @@
         <v>19.5</v>
       </c>
       <c r="BA70" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB70" t="n">
         <v>12.5</v>
@@ -14108,11 +14108,11 @@
         <v>7.6</v>
       </c>
       <c r="BG70" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14358,7 @@
         <v>1.01</v>
       </c>
       <c r="M72" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N72" t="n">
         <v>2.28</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -14531,19 +14531,19 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G73" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="H73" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="I73" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J73" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="K73" t="n">
         <v>110</v>
@@ -14552,7 +14552,7 @@
         <v>1.61</v>
       </c>
       <c r="M73" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N73" t="n">
         <v>1.98</v>
@@ -14561,7 +14561,7 @@
         <v>1.62</v>
       </c>
       <c r="P73" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Q73" t="n">
         <v>2.66</v>
@@ -14570,7 +14570,7 @@
         <v>1.1</v>
       </c>
       <c r="S73" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T73" t="n">
         <v>1.01</v>
@@ -14579,13 +14579,13 @@
         <v>1.01</v>
       </c>
       <c r="V73" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W73" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="X73" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y73" t="n">
         <v>1000</v>
@@ -14642,59 +14642,59 @@
         <v>6.2</v>
       </c>
       <c r="AQ73" t="n">
-        <v>8.4</v>
+        <v>1.11</v>
       </c>
       <c r="AR73" t="n">
-        <v>19.5</v>
+        <v>1.11</v>
       </c>
       <c r="AS73" t="n">
-        <v>40</v>
+        <v>1.11</v>
       </c>
       <c r="AT73" t="n">
-        <v>5.3</v>
+        <v>1.11</v>
       </c>
       <c r="AU73" t="n">
-        <v>5.9</v>
+        <v>1.11</v>
       </c>
       <c r="AV73" t="n">
-        <v>16.5</v>
+        <v>1.11</v>
       </c>
       <c r="AW73" t="n">
-        <v>40</v>
+        <v>1.11</v>
       </c>
       <c r="AX73" t="n">
-        <v>8.6</v>
+        <v>1.11</v>
       </c>
       <c r="AY73" t="n">
-        <v>9.6</v>
+        <v>1.11</v>
       </c>
       <c r="AZ73" t="n">
-        <v>23</v>
+        <v>1.11</v>
       </c>
       <c r="BA73" t="n">
-        <v>40</v>
+        <v>1.11</v>
       </c>
       <c r="BB73" t="n">
-        <v>19</v>
+        <v>1.11</v>
       </c>
       <c r="BC73" t="n">
-        <v>23</v>
+        <v>1.11</v>
       </c>
       <c r="BD73" t="n">
-        <v>40</v>
+        <v>1.11</v>
       </c>
       <c r="BE73" t="n">
-        <v>40</v>
+        <v>1.11</v>
       </c>
       <c r="BF73" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BG73" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -14728,22 +14728,22 @@
         <v>3.75</v>
       </c>
       <c r="G74" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="H74" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I74" t="n">
-        <v>240</v>
+        <v>2.88</v>
       </c>
       <c r="J74" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="K74" t="n">
         <v>3.6</v>
       </c>
       <c r="L74" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="M74" t="n">
         <v>1.01</v>
@@ -14752,7 +14752,7 @@
         <v>1.93</v>
       </c>
       <c r="O74" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="P74" t="n">
         <v>1.32</v>
@@ -14773,10 +14773,10 @@
         <v>1.01</v>
       </c>
       <c r="V74" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="W74" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X74" t="n">
         <v>8.4</v>
@@ -14833,7 +14833,7 @@
         <v>1000</v>
       </c>
       <c r="AP74" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.13</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -14922,7 +14922,7 @@
         <v>3.35</v>
       </c>
       <c r="G75" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H75" t="n">
         <v>2.32</v>
@@ -14931,7 +14931,7 @@
         <v>2.6</v>
       </c>
       <c r="J75" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="K75" t="n">
         <v>3.7</v>
@@ -14943,7 +14943,7 @@
         <v>1.1</v>
       </c>
       <c r="N75" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O75" t="n">
         <v>1.44</v>
@@ -14958,13 +14958,13 @@
         <v>1.18</v>
       </c>
       <c r="S75" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T75" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U75" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V75" t="n">
         <v>1.63</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G76" t="n">
         <v>1.93</v>
@@ -15122,7 +15122,7 @@
         <v>4.9</v>
       </c>
       <c r="I76" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J76" t="n">
         <v>3.4</v>
@@ -15131,7 +15131,7 @@
         <v>3.8</v>
       </c>
       <c r="L76" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M76" t="n">
         <v>1.09</v>
@@ -15152,16 +15152,16 @@
         <v>1.27</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T76" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="U76" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="V76" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W76" t="n">
         <v>2.08</v>
@@ -15182,7 +15182,7 @@
         <v>7.8</v>
       </c>
       <c r="AC76" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD76" t="n">
         <v>22</v>
@@ -15227,10 +15227,10 @@
         <v>13</v>
       </c>
       <c r="AR76" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS76" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT76" t="n">
         <v>6.6</v>
@@ -15242,7 +15242,7 @@
         <v>17.5</v>
       </c>
       <c r="AW76" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX76" t="n">
         <v>8.800000000000001</v>
@@ -15254,7 +15254,7 @@
         <v>18.5</v>
       </c>
       <c r="BA76" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB76" t="n">
         <v>17.5</v>
@@ -15263,20 +15263,20 @@
         <v>18.5</v>
       </c>
       <c r="BD76" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE76" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF76" t="n">
         <v>13.5</v>
       </c>
       <c r="BG76" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -15322,7 +15322,7 @@
         <v>3.65</v>
       </c>
       <c r="K77" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L77" t="n">
         <v>1.01</v>
@@ -15340,13 +15340,13 @@
         <v>2.06</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R77" t="n">
         <v>1.42</v>
       </c>
       <c r="S77" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T77" t="n">
         <v>1.59</v>
@@ -15373,7 +15373,7 @@
         <v>24</v>
       </c>
       <c r="AB77" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC77" t="n">
         <v>8.800000000000001</v>
@@ -15388,16 +15388,16 @@
         <v>32</v>
       </c>
       <c r="AG77" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AH77" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AI77" t="n">
         <v>34</v>
       </c>
       <c r="AJ77" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AK77" t="n">
         <v>48</v>
@@ -15412,7 +15412,7 @@
         <v>44</v>
       </c>
       <c r="AO77" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AP77" t="n">
         <v>7</v>
@@ -15424,10 +15424,10 @@
         <v>11.5</v>
       </c>
       <c r="AS77" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT77" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU77" t="n">
         <v>7.6</v>
@@ -15436,10 +15436,10 @@
         <v>9.4</v>
       </c>
       <c r="AW77" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX77" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AY77" t="n">
         <v>14.5</v>
@@ -15448,29 +15448,29 @@
         <v>15</v>
       </c>
       <c r="BA77" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB77" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD77" t="n">
         <v>9.6</v>
       </c>
-      <c r="BC77" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD77" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BE77" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF77" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG77" t="n">
         <v>10.5</v>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -15501,22 +15501,22 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G78" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="J78" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="K78" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="L78" t="n">
         <v>1.01</v>
@@ -15525,22 +15525,22 @@
         <v>1.03</v>
       </c>
       <c r="N78" t="n">
-        <v>6</v>
+        <v>2.74</v>
       </c>
       <c r="O78" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P78" t="n">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="R78" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="S78" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="T78" t="n">
         <v>1.68</v>
@@ -15549,7 +15549,7 @@
         <v>2.06</v>
       </c>
       <c r="V78" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="W78" t="n">
         <v>1.12</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -15698,7 +15698,7 @@
         <v>3.15</v>
       </c>
       <c r="G79" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="H79" t="n">
         <v>2.68</v>
@@ -15716,7 +15716,7 @@
         <v>1.01</v>
       </c>
       <c r="M79" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N79" t="n">
         <v>2.3</v>
@@ -15746,10 +15746,10 @@
         <v>1.53</v>
       </c>
       <c r="W79" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X79" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y79" t="n">
         <v>7.6</v>
@@ -15812,7 +15812,7 @@
         <v>13.5</v>
       </c>
       <c r="AS79" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT79" t="n">
         <v>7</v>
@@ -15836,29 +15836,29 @@
         <v>6.2</v>
       </c>
       <c r="BA79" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB79" t="n">
         <v>7.2</v>
       </c>
       <c r="BC79" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD79" t="n">
         <v>7.4</v>
       </c>
       <c r="BE79" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF79" t="n">
         <v>7.4</v>
       </c>
       <c r="BG79" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
         <v>85</v>
       </c>
       <c r="AJ80" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK80" t="n">
         <v>18</v>
@@ -16006,10 +16006,10 @@
         <v>40</v>
       </c>
       <c r="AS80" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="AT80" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU80" t="n">
         <v>8.199999999999999</v>
@@ -16030,7 +16030,7 @@
         <v>20</v>
       </c>
       <c r="BA80" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BB80" t="n">
         <v>15</v>
@@ -16042,7 +16042,7 @@
         <v>34</v>
       </c>
       <c r="BE80" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="BF80" t="n">
         <v>10</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -16113,25 +16113,25 @@
         <v>1.19</v>
       </c>
       <c r="P81" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q81" t="n">
         <v>1.6</v>
       </c>
       <c r="R81" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S81" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T81" t="n">
         <v>1.55</v>
       </c>
       <c r="U81" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V81" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W81" t="n">
         <v>1.8</v>
@@ -16200,7 +16200,7 @@
         <v>24</v>
       </c>
       <c r="AS81" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="AT81" t="n">
         <v>13.5</v>
@@ -16236,7 +16236,7 @@
         <v>24</v>
       </c>
       <c r="BE81" t="n">
-        <v>12.5</v>
+        <v>46</v>
       </c>
       <c r="BF81" t="n">
         <v>10</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
         <v>2.42</v>
       </c>
       <c r="O82" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P82" t="n">
         <v>1.52</v>
@@ -16325,7 +16325,7 @@
         <v>1.01</v>
       </c>
       <c r="V82" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W82" t="n">
         <v>1.58</v>
@@ -16385,52 +16385,52 @@
         <v>1000</v>
       </c>
       <c r="AP82" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ82" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR82" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS82" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AT82" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU82" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV82" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW82" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX82" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY82" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ82" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA82" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB82" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BC82" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD82" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE82" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF82" t="n">
         <v>1.01</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -16674,7 +16674,7 @@
         <v>3</v>
       </c>
       <c r="I84" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J84" t="n">
         <v>3.05</v>
@@ -16686,34 +16686,34 @@
         <v>1.01</v>
       </c>
       <c r="M84" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N84" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O84" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P84" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="R84" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="T84" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="U84" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V84" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W84" t="n">
         <v>1.56</v>
@@ -16740,7 +16740,7 @@
         <v>14.5</v>
       </c>
       <c r="AE84" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF84" t="n">
         <v>19.5</v>
@@ -16761,16 +16761,16 @@
         <v>38</v>
       </c>
       <c r="AL84" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM84" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN84" t="n">
         <v>36</v>
       </c>
       <c r="AO84" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP84" t="n">
         <v>9.6</v>
@@ -16782,7 +16782,7 @@
         <v>17.5</v>
       </c>
       <c r="AS84" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT84" t="n">
         <v>8</v>
@@ -16806,29 +16806,29 @@
         <v>16.5</v>
       </c>
       <c r="BA84" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB84" t="n">
         <v>5</v>
       </c>
-      <c r="BB84" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC84" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD84" t="n">
         <v>5</v>
       </c>
       <c r="BE84" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF84" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG84" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -17829,19 +17829,19 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="G90" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="H90" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="I90" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J90" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K90" t="n">
         <v>5.8</v>
@@ -17853,46 +17853,46 @@
         <v>1.05</v>
       </c>
       <c r="N90" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O90" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P90" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q90" t="n">
         <v>1.78</v>
       </c>
       <c r="R90" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S90" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T90" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U90" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V90" t="n">
         <v>1.08</v>
       </c>
       <c r="W90" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="X90" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y90" t="n">
         <v>34</v>
       </c>
       <c r="Z90" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA90" t="n">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="AB90" t="n">
         <v>8.4</v>
@@ -17904,7 +17904,7 @@
         <v>42</v>
       </c>
       <c r="AE90" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AF90" t="n">
         <v>8.4</v>
@@ -17916,7 +17916,7 @@
         <v>32</v>
       </c>
       <c r="AI90" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ90" t="n">
         <v>12</v>
@@ -17928,13 +17928,13 @@
         <v>44</v>
       </c>
       <c r="AM90" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN90" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO90" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AP90" t="n">
         <v>15.5</v>
@@ -17946,7 +17946,7 @@
         <v>7.8</v>
       </c>
       <c r="AS90" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT90" t="n">
         <v>6.8</v>
@@ -17958,7 +17958,7 @@
         <v>7</v>
       </c>
       <c r="AW90" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX90" t="n">
         <v>6.8</v>
@@ -17982,7 +17982,7 @@
         <v>7</v>
       </c>
       <c r="BE90" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF90" t="n">
         <v>5.5</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -18053,13 +18053,13 @@
         <v>1.38</v>
       </c>
       <c r="P91" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R91" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S91" t="n">
         <v>3.85</v>
@@ -18077,19 +18077,19 @@
         <v>1.96</v>
       </c>
       <c r="X91" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y91" t="n">
         <v>15.5</v>
       </c>
       <c r="Z91" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA91" t="n">
         <v>1000</v>
       </c>
       <c r="AB91" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC91" t="n">
         <v>8.199999999999999</v>
@@ -18119,7 +18119,7 @@
         <v>1000</v>
       </c>
       <c r="AL91" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM91" t="n">
         <v>1000</v>
@@ -18140,7 +18140,7 @@
         <v>28</v>
       </c>
       <c r="AS91" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT91" t="n">
         <v>6.8</v>
@@ -18152,7 +18152,7 @@
         <v>15.5</v>
       </c>
       <c r="AW91" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX91" t="n">
         <v>9.800000000000001</v>
@@ -18164,10 +18164,10 @@
         <v>17</v>
       </c>
       <c r="BA91" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB91" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC91" t="n">
         <v>18</v>
@@ -18176,17 +18176,17 @@
         <v>34</v>
       </c>
       <c r="BE91" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF91" t="n">
         <v>14.5</v>
       </c>
       <c r="BG91" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -18217,7 +18217,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G92" t="n">
         <v>2.5</v>
@@ -18226,7 +18226,7 @@
         <v>3.55</v>
       </c>
       <c r="I92" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J92" t="n">
         <v>3</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -18611,13 +18611,13 @@
         <v>4.1</v>
       </c>
       <c r="H94" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I94" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="J94" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K94" t="n">
         <v>3.5</v>
@@ -18626,25 +18626,25 @@
         <v>1.01</v>
       </c>
       <c r="M94" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N94" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O94" t="n">
         <v>1.42</v>
       </c>
       <c r="P94" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R94" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S94" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T94" t="n">
         <v>1.91</v>
@@ -18653,7 +18653,7 @@
         <v>1.9</v>
       </c>
       <c r="V94" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W94" t="n">
         <v>1.32</v>
@@ -18674,13 +18674,13 @@
         <v>12.5</v>
       </c>
       <c r="AC94" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD94" t="n">
         <v>12</v>
       </c>
       <c r="AE94" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF94" t="n">
         <v>28</v>
@@ -18692,13 +18692,13 @@
         <v>21</v>
       </c>
       <c r="AI94" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ94" t="n">
         <v>80</v>
       </c>
       <c r="AK94" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL94" t="n">
         <v>70</v>
@@ -18707,13 +18707,13 @@
         <v>160</v>
       </c>
       <c r="AN94" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO94" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP94" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ94" t="n">
         <v>7.2</v>
@@ -18722,7 +18722,7 @@
         <v>11.5</v>
       </c>
       <c r="AS94" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT94" t="n">
         <v>10</v>
@@ -18734,10 +18734,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW94" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX94" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY94" t="n">
         <v>13.5</v>
@@ -18746,19 +18746,19 @@
         <v>17</v>
       </c>
       <c r="BA94" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB94" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC94" t="n">
         <v>7.6</v>
       </c>
       <c r="BD94" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE94" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF94" t="n">
         <v>7.8</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -18805,7 +18805,7 @@
         <v>2.14</v>
       </c>
       <c r="H95" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I95" t="n">
         <v>4.7</v>
@@ -18814,7 +18814,7 @@
         <v>3.4</v>
       </c>
       <c r="K95" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L95" t="n">
         <v>1.01</v>
@@ -18838,7 +18838,7 @@
         <v>1.29</v>
       </c>
       <c r="S95" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T95" t="n">
         <v>1.88</v>
@@ -18850,7 +18850,7 @@
         <v>1.27</v>
       </c>
       <c r="W95" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X95" t="n">
         <v>15</v>
@@ -18862,10 +18862,10 @@
         <v>34</v>
       </c>
       <c r="AA95" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB95" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC95" t="n">
         <v>8.4</v>
@@ -18913,10 +18913,10 @@
         <v>12</v>
       </c>
       <c r="AR95" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS95" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT95" t="n">
         <v>7.2</v>
@@ -18928,7 +18928,7 @@
         <v>15</v>
       </c>
       <c r="AW95" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX95" t="n">
         <v>10</v>
@@ -18940,7 +18940,7 @@
         <v>16.5</v>
       </c>
       <c r="BA95" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB95" t="n">
         <v>20</v>
@@ -18949,20 +18949,20 @@
         <v>19</v>
       </c>
       <c r="BD95" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE95" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF95" t="n">
         <v>14.5</v>
       </c>
       <c r="BG95" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -18996,31 +18996,31 @@
         <v>1.59</v>
       </c>
       <c r="G96" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="H96" t="n">
         <v>6.6</v>
       </c>
       <c r="I96" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J96" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K96" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L96" t="n">
         <v>1.01</v>
       </c>
       <c r="M96" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N96" t="n">
         <v>3.15</v>
       </c>
       <c r="O96" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P96" t="n">
         <v>1.74</v>
@@ -19029,7 +19029,7 @@
         <v>2.16</v>
       </c>
       <c r="R96" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S96" t="n">
         <v>4</v>
@@ -19041,13 +19041,13 @@
         <v>1.73</v>
       </c>
       <c r="V96" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W96" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="X96" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y96" t="n">
         <v>20</v>
@@ -19056,7 +19056,7 @@
         <v>65</v>
       </c>
       <c r="AA96" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AB96" t="n">
         <v>7</v>
@@ -19068,7 +19068,7 @@
         <v>30</v>
       </c>
       <c r="AE96" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF96" t="n">
         <v>9</v>
@@ -19080,7 +19080,7 @@
         <v>28</v>
       </c>
       <c r="AI96" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AJ96" t="n">
         <v>16</v>
@@ -19092,13 +19092,13 @@
         <v>55</v>
       </c>
       <c r="AM96" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN96" t="n">
         <v>13</v>
       </c>
       <c r="AO96" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AP96" t="n">
         <v>10</v>
@@ -19107,10 +19107,10 @@
         <v>16</v>
       </c>
       <c r="AR96" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS96" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT96" t="n">
         <v>5.8</v>
@@ -19119,10 +19119,10 @@
         <v>7.8</v>
       </c>
       <c r="AV96" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW96" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX96" t="n">
         <v>7.4</v>
@@ -19131,10 +19131,10 @@
         <v>9</v>
       </c>
       <c r="AZ96" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA96" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB96" t="n">
         <v>13</v>
@@ -19143,20 +19143,20 @@
         <v>17</v>
       </c>
       <c r="BD96" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE96" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF96" t="n">
         <v>10</v>
       </c>
       <c r="BG96" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -19295,52 +19295,52 @@
         <v>1000</v>
       </c>
       <c r="AP97" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ97" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR97" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS97" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT97" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU97" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV97" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW97" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AX97" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY97" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ97" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA97" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB97" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BC97" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BD97" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE97" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF97" t="n">
         <v>1.01</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -19608,7 +19608,7 @@
         <v>1.73</v>
       </c>
       <c r="Q99" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R99" t="n">
         <v>1.25</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -19772,10 +19772,10 @@
         <v>2.12</v>
       </c>
       <c r="G100" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H100" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I100" t="n">
         <v>4.2</v>
@@ -19790,13 +19790,13 @@
         <v>1.01</v>
       </c>
       <c r="M100" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N100" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="O100" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="P100" t="n">
         <v>1.71</v>
@@ -19805,22 +19805,22 @@
         <v>2.22</v>
       </c>
       <c r="R100" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S100" t="n">
         <v>4.2</v>
       </c>
       <c r="T100" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="U100" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="V100" t="n">
         <v>1.32</v>
       </c>
       <c r="W100" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X100" t="n">
         <v>13.5</v>
@@ -19847,7 +19847,7 @@
         <v>70</v>
       </c>
       <c r="AF100" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG100" t="n">
         <v>13.5</v>
@@ -19859,19 +19859,19 @@
         <v>85</v>
       </c>
       <c r="AJ100" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK100" t="n">
         <v>32</v>
       </c>
       <c r="AL100" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM100" t="n">
         <v>160</v>
       </c>
       <c r="AN100" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO100" t="n">
         <v>90</v>
@@ -19886,7 +19886,7 @@
         <v>18.5</v>
       </c>
       <c r="AS100" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT100" t="n">
         <v>7.2</v>
@@ -19898,7 +19898,7 @@
         <v>14.5</v>
       </c>
       <c r="AW100" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX100" t="n">
         <v>11.5</v>
@@ -19910,29 +19910,29 @@
         <v>17</v>
       </c>
       <c r="BA100" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD100" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB100" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC100" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD100" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BE100" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF100" t="n">
         <v>16</v>
       </c>
       <c r="BG100" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="G101" t="n">
         <v>2.96</v>
@@ -19993,7 +19993,7 @@
         <v>1.32</v>
       </c>
       <c r="P101" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q101" t="n">
         <v>1.98</v>
@@ -20005,13 +20005,13 @@
         <v>3.4</v>
       </c>
       <c r="T101" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="U101" t="n">
         <v>2.18</v>
       </c>
       <c r="V101" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W101" t="n">
         <v>1.51</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -20199,10 +20199,10 @@
         <v>3.85</v>
       </c>
       <c r="T102" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="U102" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="V102" t="n">
         <v>1.38</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -20351,7 +20351,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="G103" t="n">
         <v>2.88</v>
@@ -20366,7 +20366,7 @@
         <v>1.09</v>
       </c>
       <c r="K103" t="n">
-        <v>110</v>
+        <v>3.75</v>
       </c>
       <c r="L103" t="n">
         <v>1.01</v>
@@ -20375,13 +20375,13 @@
         <v>1.01</v>
       </c>
       <c r="N103" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O103" t="n">
         <v>1.44</v>
       </c>
       <c r="P103" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q103" t="n">
         <v>1.92</v>
@@ -20399,10 +20399,10 @@
         <v>1.01</v>
       </c>
       <c r="V103" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W103" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X103" t="n">
         <v>1000</v>
@@ -20459,52 +20459,52 @@
         <v>1000</v>
       </c>
       <c r="AP103" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ103" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR103" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AS103" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AT103" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU103" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV103" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW103" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX103" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY103" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ103" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA103" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BB103" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BC103" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD103" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE103" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BF103" t="n">
         <v>1.01</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -20554,10 +20554,10 @@
         <v>2.92</v>
       </c>
       <c r="I104" t="n">
-        <v>110</v>
+        <v>4.5</v>
       </c>
       <c r="J104" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="K104" t="n">
         <v>110</v>
@@ -20593,7 +20593,7 @@
         <v>1.01</v>
       </c>
       <c r="V104" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W104" t="n">
         <v>1.51</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -20748,13 +20748,13 @@
         <v>3.8</v>
       </c>
       <c r="I105" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J105" t="n">
         <v>3.05</v>
       </c>
       <c r="K105" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L105" t="n">
         <v>1.01</v>
@@ -20763,10 +20763,10 @@
         <v>1.1</v>
       </c>
       <c r="N105" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O105" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P105" t="n">
         <v>1.64</v>
@@ -20775,7 +20775,7 @@
         <v>2.36</v>
       </c>
       <c r="R105" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S105" t="n">
         <v>4.5</v>
@@ -20784,10 +20784,10 @@
         <v>1.81</v>
       </c>
       <c r="U105" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V105" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W105" t="n">
         <v>1.74</v>
@@ -20838,7 +20838,7 @@
         <v>55</v>
       </c>
       <c r="AM105" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN105" t="n">
         <v>28</v>
@@ -20868,7 +20868,7 @@
         <v>14</v>
       </c>
       <c r="AW105" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX105" t="n">
         <v>11</v>
@@ -20880,7 +20880,7 @@
         <v>18</v>
       </c>
       <c r="BA105" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB105" t="n">
         <v>7.2</v>
@@ -20898,11 +20898,11 @@
         <v>7</v>
       </c>
       <c r="BG105" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -21145,7 +21145,7 @@
         <v>3.2</v>
       </c>
       <c r="L107" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="M107" t="n">
         <v>1.14</v>
@@ -21226,7 +21226,7 @@
         <v>75</v>
       </c>
       <c r="AM107" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN107" t="n">
         <v>48</v>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -21327,10 +21327,10 @@
         <v>1.54</v>
       </c>
       <c r="H108" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I108" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J108" t="n">
         <v>4.5</v>
@@ -21363,10 +21363,10 @@
         <v>2.88</v>
       </c>
       <c r="T108" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="U108" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V108" t="n">
         <v>1.14</v>
@@ -21393,7 +21393,7 @@
         <v>10.5</v>
       </c>
       <c r="AD108" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE108" t="n">
         <v>110</v>
@@ -21435,10 +21435,10 @@
         <v>23</v>
       </c>
       <c r="AR108" t="n">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="AS108" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT108" t="n">
         <v>8.199999999999999</v>
@@ -21450,7 +21450,7 @@
         <v>24</v>
       </c>
       <c r="AW108" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX108" t="n">
         <v>8.4</v>
@@ -21459,10 +21459,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ108" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA108" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB108" t="n">
         <v>12.5</v>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -21515,13 +21515,13 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G109" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H109" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I109" t="n">
         <v>7.2</v>
@@ -21545,13 +21545,13 @@
         <v>1.23</v>
       </c>
       <c r="P109" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q109" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R109" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S109" t="n">
         <v>2.68</v>
@@ -21566,7 +21566,7 @@
         <v>1.16</v>
       </c>
       <c r="W109" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="X109" t="n">
         <v>22</v>
@@ -21575,7 +21575,7 @@
         <v>26</v>
       </c>
       <c r="Z109" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA109" t="n">
         <v>200</v>
@@ -21587,10 +21587,10 @@
         <v>11</v>
       </c>
       <c r="AD109" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE109" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF109" t="n">
         <v>11</v>
@@ -21602,10 +21602,10 @@
         <v>22</v>
       </c>
       <c r="AI109" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ109" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK109" t="n">
         <v>17</v>
@@ -21617,7 +21617,7 @@
         <v>120</v>
       </c>
       <c r="AN109" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO109" t="n">
         <v>110</v>
@@ -21629,10 +21629,10 @@
         <v>20</v>
       </c>
       <c r="AR109" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS109" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT109" t="n">
         <v>8.4</v>
@@ -21644,7 +21644,7 @@
         <v>20</v>
       </c>
       <c r="AW109" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX109" t="n">
         <v>8.800000000000001</v>
@@ -21665,20 +21665,20 @@
         <v>13.5</v>
       </c>
       <c r="BD109" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE109" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF109" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BG109" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-05.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="G2" t="n">
         <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="J2" t="n">
         <v>4.2</v>
@@ -802,10 +802,10 @@
         <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="W2" t="n">
         <v>1.22</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="H3" t="n">
         <v>5.9</v>
@@ -963,10 +963,10 @@
         <v>6.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.27</v>
@@ -981,16 +981,16 @@
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T3" t="n">
         <v>1.65</v>
@@ -1002,7 +1002,7 @@
         <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X3" t="n">
         <v>28</v>
@@ -1014,7 +1014,7 @@
         <v>55</v>
       </c>
       <c r="AA3" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
         <v>12.5</v>
@@ -1023,7 +1023,7 @@
         <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
         <v>70</v>
@@ -1032,22 +1032,22 @@
         <v>12</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
         <v>18.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK3" t="n">
         <v>14.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM3" t="n">
         <v>70</v>
@@ -1059,16 +1059,16 @@
         <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AQ3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR3" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT3" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
         <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX3" t="n">
         <v>11</v>
@@ -1092,7 +1092,7 @@
         <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="BB3" t="n">
         <v>14.5</v>
@@ -1104,17 +1104,17 @@
         <v>22</v>
       </c>
       <c r="BE3" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -1339,118 +1339,118 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="I5" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.71</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
         <v>1.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>1.84</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V5" t="n">
         <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
         <v>1.03</v>
@@ -1459,34 +1459,34 @@
         <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AW5" t="n">
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
         <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD5" t="n">
         <v>1.03</v>
@@ -1495,14 +1495,14 @@
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>90</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G6" t="n">
         <v>2.52</v>
@@ -1551,16 +1551,16 @@
         <v>6.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
         <v>1.87</v>
@@ -1572,7 +1572,7 @@
         <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -1730,55 +1730,55 @@
         <v>2.48</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1838,59 +1838,59 @@
         <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>17.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13.5</v>
+        <v>4.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BC7" t="n">
         <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF7" t="n">
         <v>17</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
         <v>870</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
         <v>110</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
         <v>2.1</v>
@@ -2130,7 +2130,7 @@
         <v>3.95</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
         <v>1.26</v>
@@ -2160,7 +2160,7 @@
         <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V9" t="n">
         <v>1.35</v>
@@ -2184,7 +2184,7 @@
         <v>16</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
         <v>18</v>
@@ -2229,10 +2229,10 @@
         <v>17</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT9" t="n">
         <v>12</v>
@@ -2265,7 +2265,7 @@
         <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BE9" t="n">
         <v>6</v>
@@ -2274,11 +2274,11 @@
         <v>9</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H10" t="n">
         <v>3.75</v>
@@ -2321,13 +2321,13 @@
         <v>3.95</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
         <v>3.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
@@ -2357,10 +2357,10 @@
         <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X10" t="n">
         <v>16.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G11" t="n">
         <v>2.12</v>
@@ -2512,13 +2512,13 @@
         <v>4.3</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2530,7 +2530,7 @@
         <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
         <v>1.61</v>
@@ -2551,7 +2551,7 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W11" t="n">
         <v>1.89</v>
@@ -2662,11 +2662,11 @@
         <v>2.46</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>4.3</v>
       </c>
       <c r="H12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I12" t="n">
         <v>1.91</v>
@@ -2727,7 +2727,7 @@
         <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
         <v>1.61</v>
@@ -2763,10 +2763,10 @@
         <v>25</v>
       </c>
       <c r="AB12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
         <v>12.5</v>
@@ -2781,7 +2781,7 @@
         <v>20</v>
       </c>
       <c r="AH12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>32</v>
@@ -2805,10 +2805,10 @@
         <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR12" t="n">
         <v>12.5</v>
@@ -2817,7 +2817,7 @@
         <v>18</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AU12" t="n">
         <v>8.800000000000001</v>
@@ -2829,7 +2829,7 @@
         <v>15.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AY12" t="n">
         <v>15</v>
@@ -2841,26 +2841,26 @@
         <v>19.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BG12" t="n">
         <v>7.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.96</v>
       </c>
       <c r="G13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H13" t="n">
         <v>3.9</v>
@@ -2903,7 +2903,7 @@
         <v>4.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K13" t="n">
         <v>4.1</v>
@@ -2921,7 +2921,7 @@
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
         <v>1.76</v>
@@ -2942,7 +2942,7 @@
         <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="X13" t="n">
         <v>19.5</v>
@@ -2963,7 +2963,7 @@
         <v>9</v>
       </c>
       <c r="AD13" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE13" t="n">
         <v>48</v>
@@ -3008,7 +3008,7 @@
         <v>23</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT13" t="n">
         <v>9.800000000000001</v>
@@ -3020,7 +3020,7 @@
         <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="AX13" t="n">
         <v>11.5</v>
@@ -3032,7 +3032,7 @@
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB13" t="n">
         <v>19.5</v>
@@ -3044,17 +3044,17 @@
         <v>23</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13" t="n">
         <v>10</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -3109,22 +3109,22 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.22</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R14" t="n">
         <v>1.52</v>
       </c>
       <c r="S14" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T14" t="n">
         <v>1.61</v>
@@ -3178,7 +3178,7 @@
         <v>32</v>
       </c>
       <c r="AK14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL14" t="n">
         <v>32</v>
@@ -3202,7 +3202,7 @@
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT14" t="n">
         <v>11.5</v>
@@ -3214,7 +3214,7 @@
         <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX14" t="n">
         <v>14.5</v>
@@ -3226,7 +3226,7 @@
         <v>13.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BB14" t="n">
         <v>23</v>
@@ -3238,7 +3238,7 @@
         <v>23</v>
       </c>
       <c r="BE14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14" t="n">
         <v>11.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>1.53</v>
       </c>
       <c r="G15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H15" t="n">
         <v>7</v>
@@ -3312,7 +3312,7 @@
         <v>2.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R15" t="n">
         <v>1.56</v>
@@ -3324,16 +3324,16 @@
         <v>1.78</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V15" t="n">
         <v>1.16</v>
       </c>
       <c r="W15" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="X15" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Y15" t="n">
         <v>27</v>
@@ -3360,7 +3360,7 @@
         <v>11</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
         <v>21</v>
@@ -3393,10 +3393,10 @@
         <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
         <v>9.4</v>
@@ -3408,7 +3408,7 @@
         <v>18.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX15" t="n">
         <v>9.4</v>
@@ -3420,7 +3420,7 @@
         <v>18</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB15" t="n">
         <v>12.5</v>
@@ -3432,17 +3432,17 @@
         <v>21</v>
       </c>
       <c r="BE15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF15" t="n">
         <v>5.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         <v>2.56</v>
       </c>
       <c r="G16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H16" t="n">
         <v>2.72</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2.7</v>
       </c>
       <c r="I16" t="n">
         <v>2.86</v>
@@ -3518,7 +3518,7 @@
         <v>1.68</v>
       </c>
       <c r="U16" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V16" t="n">
         <v>1.53</v>
@@ -3542,7 +3542,7 @@
         <v>13.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
         <v>13.5</v>
@@ -3551,7 +3551,7 @@
         <v>32</v>
       </c>
       <c r="AF16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG16" t="n">
         <v>13</v>
@@ -3575,7 +3575,7 @@
         <v>80</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>23</v>
@@ -3590,7 +3590,7 @@
         <v>16.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT16" t="n">
         <v>10.5</v>
@@ -3614,19 +3614,19 @@
         <v>13.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC16" t="n">
         <v>19</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF16" t="n">
         <v>17</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>3.7</v>
       </c>
       <c r="G17" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H17" t="n">
         <v>1.64</v>
@@ -3679,16 +3679,16 @@
         <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.95</v>
+        <v>2.96</v>
       </c>
       <c r="K17" t="n">
-        <v>8.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
         <v>1.02</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G18" t="n">
         <v>1.8</v>
@@ -3870,13 +3870,13 @@
         <v>5.7</v>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="J18" t="n">
         <v>2.86</v>
       </c>
       <c r="K18" t="n">
-        <v>6.4</v>
+        <v>85</v>
       </c>
       <c r="L18" t="n">
         <v>1.44</v>
@@ -3909,7 +3909,7 @@
         <v>1.61</v>
       </c>
       <c r="V18" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W18" t="n">
         <v>2.24</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -4055,145 +4055,145 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="G19" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="H19" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="K19" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="L19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.43</v>
       </c>
-      <c r="M19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.41</v>
-      </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AS19" t="n">
         <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AW19" t="n">
         <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
         <v>1.03</v>
@@ -4211,14 +4211,14 @@
         <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -4267,49 +4267,49 @@
         <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P20" t="n">
         <v>1.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T20" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="U20" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
         <v>2.24</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y20" t="n">
         <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA20" t="n">
         <v>19</v>
@@ -4318,7 +4318,7 @@
         <v>19.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD20" t="n">
         <v>10.5</v>
@@ -4354,7 +4354,7 @@
         <v>110</v>
       </c>
       <c r="AO20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP20" t="n">
         <v>13</v>
@@ -4363,7 +4363,7 @@
         <v>7.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS20" t="n">
         <v>15.5</v>
@@ -4372,16 +4372,16 @@
         <v>15.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW20" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY20" t="n">
         <v>17.5</v>
@@ -4390,29 +4390,29 @@
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB20" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BE20" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BG20" t="n">
         <v>9.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
         <v>2.64</v>
       </c>
       <c r="O21" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P21" t="n">
         <v>2.24</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
         <v>1.38</v>
       </c>
       <c r="R22" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="S22" t="n">
         <v>2.12</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
         <v>4.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P23" t="n">
         <v>2.06</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="G24" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="H24" t="n">
         <v>3.55</v>
       </c>
       <c r="I24" t="n">
-        <v>5.3</v>
+        <v>110</v>
       </c>
       <c r="J24" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="K24" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.36</v>
@@ -5049,19 +5049,19 @@
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="O24" t="n">
         <v>1.28</v>
       </c>
       <c r="P24" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="R24" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
         <v>3.05</v>
@@ -5073,10 +5073,10 @@
         <v>1.92</v>
       </c>
       <c r="V24" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W24" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5136,7 +5136,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR24" t="n">
         <v>1.01</v>
@@ -5145,31 +5145,31 @@
         <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW24" t="n">
         <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA24" t="n">
         <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
         <v>1.01</v>
@@ -5181,14 +5181,14 @@
         <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG24" t="n">
         <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H25" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="I25" t="n">
         <v>1.7</v>
@@ -5234,10 +5234,10 @@
         <v>4.1</v>
       </c>
       <c r="K25" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
@@ -5249,16 +5249,16 @@
         <v>1.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R25" t="n">
         <v>1.45</v>
       </c>
       <c r="S25" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T25" t="n">
         <v>1.77</v>
@@ -5270,58 +5270,58 @@
         <v>2.42</v>
       </c>
       <c r="W25" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AC25" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AF25" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ25" t="n">
         <v>170</v>
       </c>
       <c r="AK25" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AL25" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM25" t="n">
         <v>120</v>
       </c>
       <c r="AN25" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AO25" t="n">
         <v>9.199999999999999</v>
@@ -5351,7 +5351,7 @@
         <v>14</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AY25" t="n">
         <v>18.5</v>
@@ -5360,29 +5360,29 @@
         <v>16.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G26" t="n">
         <v>1.54</v>
       </c>
       <c r="H26" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
         <v>6.6</v>
@@ -5428,7 +5428,7 @@
         <v>5.2</v>
       </c>
       <c r="K26" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5443,7 +5443,7 @@
         <v>1.16</v>
       </c>
       <c r="P26" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Q26" t="n">
         <v>1.48</v>
@@ -5458,16 +5458,16 @@
         <v>1.66</v>
       </c>
       <c r="U26" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W26" t="n">
         <v>2.84</v>
       </c>
       <c r="X26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y26" t="n">
         <v>34</v>
@@ -5482,22 +5482,22 @@
         <v>14</v>
       </c>
       <c r="AC26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE26" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF26" t="n">
         <v>12.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI26" t="n">
         <v>60</v>
@@ -5506,43 +5506,43 @@
         <v>16</v>
       </c>
       <c r="AK26" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM26" t="n">
         <v>75</v>
       </c>
       <c r="AN26" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.6</v>
+        <v>26</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="AR26" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AS26" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU26" t="n">
         <v>11.5</v>
       </c>
       <c r="AV26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX26" t="n">
         <v>10.5</v>
@@ -5554,10 +5554,10 @@
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC26" t="n">
         <v>12.5</v>
@@ -5566,17 +5566,17 @@
         <v>21</v>
       </c>
       <c r="BE26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BF26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -5607,19 +5607,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="G27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H27" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="I27" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J27" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
         <v>5.4</v>
@@ -5652,13 +5652,13 @@
         <v>1.65</v>
       </c>
       <c r="U27" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V27" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="W27" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
         <v>34</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -5825,13 +5825,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="O28" t="n">
         <v>1.26</v>
       </c>
       <c r="P28" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q28" t="n">
         <v>1.71</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -5998,13 +5998,13 @@
         <v>3.75</v>
       </c>
       <c r="G29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H29" t="n">
         <v>2.2</v>
       </c>
       <c r="I29" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J29" t="n">
         <v>3.5</v>
@@ -6019,13 +6019,13 @@
         <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
         <v>1.36</v>
       </c>
       <c r="P29" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q29" t="n">
         <v>2.1</v>
@@ -6073,7 +6073,7 @@
         <v>24</v>
       </c>
       <c r="AF29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG29" t="n">
         <v>15.5</v>
@@ -6139,13 +6139,13 @@
         <v>36</v>
       </c>
       <c r="BB29" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC29" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BD29" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BE29" t="n">
         <v>40</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -6195,49 +6195,49 @@
         <v>5.5</v>
       </c>
       <c r="H30" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="I30" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="J30" t="n">
         <v>3.7</v>
       </c>
       <c r="K30" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
         <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P30" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R30" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
         <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U30" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V30" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="W30" t="n">
         <v>1.22</v>
@@ -6249,7 +6249,7 @@
         <v>7.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA30" t="n">
         <v>19</v>
@@ -6264,7 +6264,7 @@
         <v>10</v>
       </c>
       <c r="AE30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF30" t="n">
         <v>40</v>
@@ -6273,25 +6273,25 @@
         <v>21</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI30" t="n">
         <v>44</v>
       </c>
       <c r="AJ30" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AK30" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AL30" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AM30" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN30" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AO30" t="n">
         <v>15</v>
@@ -6300,19 +6300,19 @@
         <v>10.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR30" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS30" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AT30" t="n">
         <v>14</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV30" t="n">
         <v>9.4</v>
@@ -6348,11 +6348,11 @@
         <v>40</v>
       </c>
       <c r="BG30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -6383,170 +6383,170 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G31" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H31" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I31" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X31" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR31" t="n">
         <v>4</v>
       </c>
-      <c r="K31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J32" t="n">
         <v>4.1</v>
       </c>
-      <c r="G32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="I32" t="n">
-        <v>110</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.54</v>
-      </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -6613,10 +6613,10 @@
         <v>1.72</v>
       </c>
       <c r="R32" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="T32" t="n">
         <v>1.66</v>
@@ -6625,10 +6625,10 @@
         <v>1.87</v>
       </c>
       <c r="V32" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="W32" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G33" t="n">
         <v>2.2</v>
@@ -6789,7 +6789,7 @@
         <v>3.35</v>
       </c>
       <c r="L33" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M33" t="n">
         <v>1.12</v>
@@ -6798,25 +6798,25 @@
         <v>2.76</v>
       </c>
       <c r="O33" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P33" t="n">
         <v>1.59</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R33" t="n">
         <v>1.21</v>
       </c>
       <c r="S33" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T33" t="n">
         <v>2.22</v>
       </c>
       <c r="U33" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V33" t="n">
         <v>1.31</v>
@@ -6837,7 +6837,7 @@
         <v>100</v>
       </c>
       <c r="AB33" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC33" t="n">
         <v>7.6</v>
@@ -6855,13 +6855,13 @@
         <v>11.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI33" t="n">
         <v>95</v>
       </c>
       <c r="AJ33" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK33" t="n">
         <v>30</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>1.94</v>
       </c>
       <c r="G34" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="H34" t="n">
         <v>3.3</v>
@@ -7016,7 +7016,7 @@
         <v>1.23</v>
       </c>
       <c r="W34" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -7159,31 +7159,31 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="G35" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="H35" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="I35" t="n">
-        <v>1000</v>
+        <v>1.97</v>
       </c>
       <c r="J35" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K35" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N35" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="O35" t="n">
         <v>1.4</v>
@@ -7192,79 +7192,79 @@
         <v>1.78</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="R35" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S35" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP35" t="n">
         <v>1.03</v>
@@ -7318,11 +7318,11 @@
         <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -7353,25 +7353,25 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H36" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="I36" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="J36" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L36" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M36" t="n">
         <v>1.01</v>
@@ -7401,10 +7401,10 @@
         <v>1.48</v>
       </c>
       <c r="V36" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="W36" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -7550,19 +7550,19 @@
         <v>2.26</v>
       </c>
       <c r="G37" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="H37" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="I37" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K37" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7571,7 +7571,7 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O37" t="n">
         <v>1.01</v>
@@ -7586,7 +7586,7 @@
         <v>1.29</v>
       </c>
       <c r="S37" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="T37" t="n">
         <v>1.6</v>
@@ -7598,7 +7598,7 @@
         <v>1.43</v>
       </c>
       <c r="W37" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
         <v>6.2</v>
       </c>
       <c r="H38" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="I38" t="n">
         <v>2</v>
@@ -7756,7 +7756,7 @@
         <v>3.7</v>
       </c>
       <c r="K38" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7777,10 +7777,10 @@
         <v>1.11</v>
       </c>
       <c r="R38" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S38" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G39" t="n">
         <v>2.54</v>
@@ -7947,13 +7947,13 @@
         <v>3.6</v>
       </c>
       <c r="J39" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K39" t="n">
         <v>3.6</v>
       </c>
       <c r="L39" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M39" t="n">
         <v>1.08</v>
@@ -7962,7 +7962,7 @@
         <v>3.25</v>
       </c>
       <c r="O39" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P39" t="n">
         <v>1.78</v>
@@ -7971,7 +7971,7 @@
         <v>2.08</v>
       </c>
       <c r="R39" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
         <v>3.75</v>
@@ -7998,7 +7998,7 @@
         <v>28</v>
       </c>
       <c r="AA39" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB39" t="n">
         <v>11.5</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -8144,10 +8144,10 @@
         <v>3</v>
       </c>
       <c r="K40" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L40" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="M40" t="n">
         <v>1.11</v>
@@ -8159,7 +8159,7 @@
         <v>1.48</v>
       </c>
       <c r="P40" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q40" t="n">
         <v>2.42</v>
@@ -8171,70 +8171,70 @@
         <v>4.7</v>
       </c>
       <c r="T40" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U40" t="n">
         <v>1.86</v>
       </c>
       <c r="V40" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W40" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X40" t="n">
         <v>11.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z40" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA40" t="n">
         <v>80</v>
       </c>
       <c r="AB40" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD40" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF40" t="n">
         <v>18</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL40" t="n">
         <v>60</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>70</v>
       </c>
       <c r="AM40" t="n">
         <v>190</v>
       </c>
       <c r="AN40" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AO40" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP40" t="n">
         <v>8.6</v>
@@ -8246,7 +8246,7 @@
         <v>18.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT40" t="n">
         <v>7</v>
@@ -8258,7 +8258,7 @@
         <v>12.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX40" t="n">
         <v>13</v>
@@ -8270,29 +8270,29 @@
         <v>18</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB40" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BC40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF40" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -8329,13 +8329,13 @@
         <v>2.26</v>
       </c>
       <c r="H41" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="I41" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J41" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K41" t="n">
         <v>6.4</v>
@@ -8371,7 +8371,7 @@
         <v>1.01</v>
       </c>
       <c r="V41" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W41" t="n">
         <v>1.79</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -8559,10 +8559,10 @@
         <v>2.18</v>
       </c>
       <c r="T42" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="U42" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V42" t="n">
         <v>1.24</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
         <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO43" t="n">
         <v>1000</v>
@@ -8825,10 +8825,10 @@
         <v>13</v>
       </c>
       <c r="AR43" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS43" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT43" t="n">
         <v>7.2</v>
@@ -8840,7 +8840,7 @@
         <v>15.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX43" t="n">
         <v>9.6</v>
@@ -8852,7 +8852,7 @@
         <v>17</v>
       </c>
       <c r="BA43" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB43" t="n">
         <v>18</v>
@@ -8861,20 +8861,20 @@
         <v>17.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE43" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF43" t="n">
         <v>10.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -8905,19 +8905,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G44" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H44" t="n">
         <v>2.86</v>
       </c>
       <c r="I44" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J44" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K44" t="n">
         <v>3.75</v>
@@ -8938,7 +8938,7 @@
         <v>2.06</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R44" t="n">
         <v>1.41</v>
@@ -8950,13 +8950,13 @@
         <v>1.7</v>
       </c>
       <c r="U44" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V44" t="n">
         <v>1.51</v>
       </c>
       <c r="W44" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X44" t="n">
         <v>18</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -9487,22 +9487,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="G47" t="n">
-        <v>2.9</v>
+        <v>60</v>
       </c>
       <c r="H47" t="n">
         <v>2.92</v>
       </c>
       <c r="I47" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="J47" t="n">
         <v>1.09</v>
       </c>
       <c r="K47" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9520,7 +9520,7 @@
         <v>1.81</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R47" t="n">
         <v>1.32</v>
@@ -9535,10 +9535,10 @@
         <v>1.96</v>
       </c>
       <c r="V47" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W47" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="G48" t="n">
         <v>1.67</v>
@@ -9690,13 +9690,13 @@
         <v>6.8</v>
       </c>
       <c r="I48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J48" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K48" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="L48" t="n">
         <v>1.51</v>
@@ -9732,7 +9732,7 @@
         <v>1.08</v>
       </c>
       <c r="W48" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9881,7 @@
         <v>7</v>
       </c>
       <c r="H49" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="I49" t="n">
         <v>1.75</v>
@@ -9890,7 +9890,7 @@
         <v>3.65</v>
       </c>
       <c r="K49" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -9908,13 +9908,13 @@
         <v>2.06</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R49" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="S49" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T49" t="n">
         <v>1.01</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
         <v>2.6</v>
       </c>
       <c r="G50" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H50" t="n">
         <v>3.2</v>
@@ -10105,7 +10105,7 @@
         <v>2.38</v>
       </c>
       <c r="R50" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S50" t="n">
         <v>4.7</v>
@@ -10114,13 +10114,13 @@
         <v>2.02</v>
       </c>
       <c r="U50" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V50" t="n">
         <v>1.44</v>
       </c>
       <c r="W50" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X50" t="n">
         <v>10</v>
@@ -10198,7 +10198,7 @@
         <v>13</v>
       </c>
       <c r="AW50" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX50" t="n">
         <v>14.5</v>
@@ -10222,17 +10222,17 @@
         <v>46</v>
       </c>
       <c r="BE50" t="n">
-        <v>18.5</v>
+        <v>44</v>
       </c>
       <c r="BF50" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BG50" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
         <v>2.66</v>
       </c>
       <c r="I51" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J51" t="n">
         <v>3.3</v>
@@ -10281,7 +10281,7 @@
         <v>3.35</v>
       </c>
       <c r="L51" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M51" t="n">
         <v>1.09</v>
@@ -10296,7 +10296,7 @@
         <v>1.76</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R51" t="n">
         <v>1.28</v>
@@ -10419,14 +10419,14 @@
         <v>40</v>
       </c>
       <c r="BF51" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BG51" t="n">
         <v>23</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
         <v>2.32</v>
       </c>
       <c r="G52" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H52" t="n">
         <v>3.45</v>
@@ -10508,7 +10508,7 @@
         <v>1.39</v>
       </c>
       <c r="W52" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X52" t="n">
         <v>12</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -10654,16 +10654,16 @@
         <v>1.5</v>
       </c>
       <c r="G53" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H53" t="n">
         <v>6.6</v>
       </c>
       <c r="I53" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="K53" t="n">
         <v>5</v>
@@ -10684,7 +10684,7 @@
         <v>2.52</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R53" t="n">
         <v>1.63</v>
@@ -10699,13 +10699,13 @@
         <v>2.22</v>
       </c>
       <c r="V53" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W53" t="n">
         <v>2.8</v>
       </c>
       <c r="X53" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y53" t="n">
         <v>34</v>
@@ -10732,16 +10732,16 @@
         <v>11.5</v>
       </c>
       <c r="AG53" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH53" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI53" t="n">
         <v>80</v>
       </c>
       <c r="AJ53" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK53" t="n">
         <v>16</v>
@@ -10759,16 +10759,16 @@
         <v>85</v>
       </c>
       <c r="AP53" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ53" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR53" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS53" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT53" t="n">
         <v>10</v>
@@ -10777,22 +10777,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV53" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AW53" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX53" t="n">
         <v>9.6</v>
       </c>
       <c r="AY53" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ53" t="n">
         <v>16.5</v>
       </c>
       <c r="BA53" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB53" t="n">
         <v>13</v>
@@ -10801,20 +10801,20 @@
         <v>12.5</v>
       </c>
       <c r="BD53" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE53" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF53" t="n">
         <v>5.3</v>
       </c>
       <c r="BG53" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
         <v>15</v>
       </c>
       <c r="AE54" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF54" t="n">
         <v>14.5</v>
@@ -11004,11 +11004,11 @@
         <v>11</v>
       </c>
       <c r="BG54" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -11039,22 +11039,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="G55" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="H55" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="I55" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="J55" t="n">
         <v>3.1</v>
       </c>
       <c r="K55" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="L55" t="n">
         <v>1.34</v>
@@ -11063,22 +11063,22 @@
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>2.82</v>
+        <v>3.35</v>
       </c>
       <c r="O55" t="n">
         <v>1.32</v>
       </c>
       <c r="P55" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="Q55" t="n">
         <v>1.96</v>
       </c>
       <c r="R55" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S55" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T55" t="n">
         <v>1.01</v>
@@ -11087,10 +11087,10 @@
         <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="W55" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -11254,31 +11254,31 @@
         <v>1.01</v>
       </c>
       <c r="M56" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N56" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="O56" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P56" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="Q56" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R56" t="n">
         <v>1.51</v>
       </c>
-      <c r="R56" t="n">
-        <v>1.44</v>
-      </c>
       <c r="S56" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="T56" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="U56" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="V56" t="n">
         <v>1.92</v>
@@ -11287,116 +11287,116 @@
         <v>1.32</v>
       </c>
       <c r="X56" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Y56" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Z56" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AA56" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF56" t="n">
         <v>34</v>
       </c>
-      <c r="AB56" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD56" t="n">
+      <c r="AG56" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT56" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE56" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>2.54</v>
-      </c>
       <c r="AU56" t="n">
-        <v>2.34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW56" t="n">
-        <v>2.54</v>
+        <v>16</v>
       </c>
       <c r="AX56" t="n">
-        <v>2.64</v>
+        <v>6.8</v>
       </c>
       <c r="AY56" t="n">
-        <v>2.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ56" t="n">
-        <v>2.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>2.64</v>
+        <v>6.6</v>
       </c>
       <c r="BB56" t="n">
-        <v>2.72</v>
+        <v>7.6</v>
       </c>
       <c r="BC56" t="n">
-        <v>2.68</v>
+        <v>7</v>
       </c>
       <c r="BD56" t="n">
-        <v>2.68</v>
+        <v>7</v>
       </c>
       <c r="BE56" t="n">
-        <v>2.72</v>
+        <v>7.6</v>
       </c>
       <c r="BF56" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="BG56" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -11445,34 +11445,34 @@
         <v>3.1</v>
       </c>
       <c r="L57" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M57" t="n">
         <v>1.11</v>
       </c>
       <c r="N57" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O57" t="n">
         <v>1.46</v>
       </c>
       <c r="P57" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R57" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S57" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T57" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U57" t="n">
         <v>1.98</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.96</v>
       </c>
       <c r="V57" t="n">
         <v>1.59</v>
@@ -11499,7 +11499,7 @@
         <v>6.8</v>
       </c>
       <c r="AD57" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE57" t="n">
         <v>34</v>
@@ -11511,7 +11511,7 @@
         <v>14.5</v>
       </c>
       <c r="AH57" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI57" t="n">
         <v>55</v>
@@ -11523,10 +11523,10 @@
         <v>44</v>
       </c>
       <c r="AL57" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM57" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN57" t="n">
         <v>50</v>
@@ -11535,10 +11535,10 @@
         <v>34</v>
       </c>
       <c r="AP57" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ57" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR57" t="n">
         <v>14.5</v>
@@ -11577,20 +11577,20 @@
         <v>38</v>
       </c>
       <c r="BD57" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BE57" t="n">
         <v>42</v>
       </c>
       <c r="BF57" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="BG57" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -11729,52 +11729,52 @@
         <v>1000</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF58" t="n">
         <v>1.01</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -11830,7 +11830,7 @@
         <v>3</v>
       </c>
       <c r="K59" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L59" t="n">
         <v>1.01</v>
@@ -11860,13 +11860,13 @@
         <v>1.75</v>
       </c>
       <c r="U59" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="V59" t="n">
         <v>1.39</v>
       </c>
       <c r="W59" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -12206,19 +12206,19 @@
         <v>1.75</v>
       </c>
       <c r="G61" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="H61" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="I61" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J61" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K61" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -12236,7 +12236,7 @@
         <v>1.59</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R61" t="n">
         <v>1.22</v>
@@ -12251,10 +12251,10 @@
         <v>1.65</v>
       </c>
       <c r="V61" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W61" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="X61" t="n">
         <v>1000</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -12400,16 +12400,16 @@
         <v>1.48</v>
       </c>
       <c r="G62" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H62" t="n">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="I62" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="J62" t="n">
-        <v>2.94</v>
+        <v>3.7</v>
       </c>
       <c r="K62" t="n">
         <v>8.800000000000001</v>
@@ -12430,7 +12430,7 @@
         <v>2.22</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R62" t="n">
         <v>1.38</v>
@@ -12448,7 +12448,7 @@
         <v>1.1</v>
       </c>
       <c r="W62" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="X62" t="n">
         <v>1000</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
         <v>1.37</v>
       </c>
       <c r="H63" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="I63" t="n">
         <v>12</v>
@@ -12615,10 +12615,10 @@
         <v>1.02</v>
       </c>
       <c r="N63" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="O63" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P63" t="n">
         <v>2.8</v>
@@ -12627,16 +12627,16 @@
         <v>1.46</v>
       </c>
       <c r="R63" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="S63" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="T63" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U63" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V63" t="n">
         <v>1.09</v>
@@ -12645,116 +12645,116 @@
         <v>3.7</v>
       </c>
       <c r="X63" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Y63" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="Z63" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA63" t="n">
         <v>1000</v>
       </c>
       <c r="AB63" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC63" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AD63" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AE63" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF63" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AG63" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH63" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AI63" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ63" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AK63" t="n">
         <v>970</v>
       </c>
       <c r="AL63" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AM63" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN63" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="AO63" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP63" t="n">
-        <v>2.74</v>
+        <v>7.8</v>
       </c>
       <c r="AQ63" t="n">
-        <v>2.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR63" t="n">
-        <v>2.94</v>
+        <v>2.28</v>
       </c>
       <c r="AS63" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="AU63" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AV63" t="n">
-        <v>2.78</v>
+        <v>7.8</v>
       </c>
       <c r="AW63" t="n">
         <v>2.94</v>
       </c>
       <c r="AX63" t="n">
-        <v>2.42</v>
+        <v>5.1</v>
       </c>
       <c r="AY63" t="n">
-        <v>2.46</v>
+        <v>5.3</v>
       </c>
       <c r="AZ63" t="n">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="BA63" t="n">
-        <v>2.94</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB63" t="n">
-        <v>2.48</v>
+        <v>5.4</v>
       </c>
       <c r="BC63" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BD63" t="n">
-        <v>2.74</v>
+        <v>7.6</v>
       </c>
       <c r="BE63" t="n">
-        <v>2.94</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF63" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="BG63" t="n">
         <v>2.94</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -12785,22 +12785,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="G64" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="H64" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="I64" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J64" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="K64" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="L64" t="n">
         <v>1.01</v>
@@ -12809,13 +12809,13 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="O64" t="n">
         <v>1.64</v>
       </c>
       <c r="P64" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q64" t="n">
         <v>2.78</v>
@@ -12833,10 +12833,10 @@
         <v>1.01</v>
       </c>
       <c r="V64" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W64" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="X64" t="n">
         <v>1000</v>
@@ -12893,52 +12893,52 @@
         <v>1000</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF64" t="n">
         <v>1.01</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -12979,46 +12979,46 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="G65" t="n">
-        <v>1000</v>
+        <v>1.89</v>
       </c>
       <c r="H65" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="I65" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J65" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="K65" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="L65" t="n">
         <v>1.01</v>
       </c>
       <c r="M65" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N65" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="O65" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="P65" t="n">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.54</v>
+        <v>2.38</v>
       </c>
       <c r="R65" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S65" t="n">
-        <v>1.54</v>
+        <v>2.78</v>
       </c>
       <c r="T65" t="n">
         <v>1.01</v>
@@ -13027,10 +13027,10 @@
         <v>1.01</v>
       </c>
       <c r="V65" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W65" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X65" t="n">
         <v>1000</v>
@@ -13087,52 +13087,52 @@
         <v>1000</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF65" t="n">
         <v>1.01</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -13173,67 +13173,67 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="G66" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="H66" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="I66" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J66" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K66" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="L66" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M66" t="n">
         <v>1.07</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O66" t="n">
         <v>1.39</v>
       </c>
       <c r="P66" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R66" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S66" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="T66" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="U66" t="n">
         <v>1.41</v>
       </c>
       <c r="V66" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W66" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="X66" t="n">
         <v>15.5</v>
       </c>
       <c r="Y66" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="Z66" t="n">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="AA66" t="n">
         <v>1000</v>
@@ -13245,98 +13245,98 @@
         <v>17.5</v>
       </c>
       <c r="AD66" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AE66" t="n">
         <v>1000</v>
       </c>
       <c r="AF66" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AG66" t="n">
         <v>15.5</v>
       </c>
       <c r="AH66" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AI66" t="n">
         <v>1000</v>
       </c>
       <c r="AJ66" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK66" t="n">
         <v>25</v>
       </c>
       <c r="AL66" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM66" t="n">
         <v>1000</v>
       </c>
       <c r="AN66" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO66" t="n">
         <v>1000</v>
       </c>
       <c r="AP66" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ66" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AR66" t="n">
-        <v>170</v>
+        <v>1.03</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT66" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU66" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV66" t="n">
-        <v>60</v>
+        <v>1.03</v>
       </c>
       <c r="AW66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX66" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AY66" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ66" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="BA66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB66" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC66" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD66" t="n">
-        <v>60</v>
+        <v>1.03</v>
       </c>
       <c r="BE66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF66" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BG66" t="n">
         <v>1.01</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -13367,46 +13367,46 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="G67" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="H67" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="I67" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="K67" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L67" t="n">
         <v>1.01</v>
       </c>
       <c r="M67" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N67" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="O67" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="P67" t="n">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.54</v>
+        <v>2.62</v>
       </c>
       <c r="R67" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S67" t="n">
-        <v>1.54</v>
+        <v>2.62</v>
       </c>
       <c r="T67" t="n">
         <v>1.01</v>
@@ -13415,10 +13415,10 @@
         <v>1.01</v>
       </c>
       <c r="V67" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="W67" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="X67" t="n">
         <v>1000</v>
@@ -13475,52 +13475,52 @@
         <v>1000</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF67" t="n">
         <v>1.01</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G68" t="n">
         <v>2.02</v>
@@ -13591,7 +13591,7 @@
         <v>1.32</v>
       </c>
       <c r="P68" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q68" t="n">
         <v>1.94</v>
@@ -13669,52 +13669,52 @@
         <v>1000</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF68" t="n">
         <v>1.01</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -13791,10 +13791,10 @@
         <v>1.54</v>
       </c>
       <c r="R69" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S69" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="T69" t="n">
         <v>1.01</v>
@@ -13863,52 +13863,52 @@
         <v>1000</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF69" t="n">
         <v>1.01</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -14146,58 +14146,58 @@
         <v>1.57</v>
       </c>
       <c r="G71" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H71" t="n">
         <v>7.2</v>
       </c>
       <c r="I71" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J71" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K71" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L71" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M71" t="n">
         <v>1.06</v>
       </c>
       <c r="N71" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O71" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P71" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R71" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S71" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T71" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="U71" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="V71" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W71" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="X71" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y71" t="n">
         <v>25</v>
@@ -14206,13 +14206,13 @@
         <v>70</v>
       </c>
       <c r="AA71" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AB71" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC71" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD71" t="n">
         <v>30</v>
@@ -14221,13 +14221,13 @@
         <v>140</v>
       </c>
       <c r="AF71" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG71" t="n">
         <v>10</v>
       </c>
       <c r="AH71" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AI71" t="n">
         <v>130</v>
@@ -14236,7 +14236,7 @@
         <v>15</v>
       </c>
       <c r="AK71" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL71" t="n">
         <v>38</v>
@@ -14245,7 +14245,7 @@
         <v>150</v>
       </c>
       <c r="AN71" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO71" t="n">
         <v>190</v>
@@ -14254,37 +14254,37 @@
         <v>13.5</v>
       </c>
       <c r="AQ71" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AR71" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW71" t="n">
         <v>10</v>
       </c>
-      <c r="AS71" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT71" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU71" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV71" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW71" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AX71" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY71" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ71" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA71" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB71" t="n">
         <v>12.5</v>
@@ -14293,20 +14293,20 @@
         <v>14.5</v>
       </c>
       <c r="BD71" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BE71" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF71" t="n">
         <v>7.8</v>
       </c>
       <c r="BG71" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -14337,31 +14337,31 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G72" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="H72" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="I72" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="J72" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K72" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="L72" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N72" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="O72" t="n">
         <v>1.24</v>
@@ -14370,25 +14370,25 @@
         <v>2.1</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R72" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="S72" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="T72" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U72" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V72" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W72" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="X72" t="n">
         <v>1000</v>
@@ -14445,52 +14445,52 @@
         <v>1000</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF72" t="n">
         <v>1.01</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -14531,13 +14531,13 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="G73" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H73" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I73" t="n">
         <v>7.4</v>
@@ -14546,7 +14546,7 @@
         <v>3.95</v>
       </c>
       <c r="K73" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="L73" t="n">
         <v>1.01</v>
@@ -14639,52 +14639,52 @@
         <v>1000</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE73" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF73" t="n">
         <v>1.01</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -14731,7 +14731,7 @@
         <v>2.3</v>
       </c>
       <c r="H74" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="I74" t="n">
         <v>5.1</v>
@@ -14740,7 +14740,7 @@
         <v>3</v>
       </c>
       <c r="K74" t="n">
-        <v>6.4</v>
+        <v>110</v>
       </c>
       <c r="L74" t="n">
         <v>1.61</v>
@@ -14833,7 +14833,7 @@
         <v>1000</v>
       </c>
       <c r="AP74" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.11</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -14919,7 +14919,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="G75" t="n">
         <v>6.6</v>
@@ -14934,7 +14934,7 @@
         <v>2</v>
       </c>
       <c r="K75" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="L75" t="n">
         <v>1.01</v>
@@ -14946,7 +14946,7 @@
         <v>1.98</v>
       </c>
       <c r="O75" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="P75" t="n">
         <v>1.32</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -15116,22 +15116,22 @@
         <v>3.35</v>
       </c>
       <c r="G76" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H76" t="n">
         <v>2.36</v>
       </c>
       <c r="I76" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="J76" t="n">
         <v>3.1</v>
       </c>
       <c r="K76" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L76" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M76" t="n">
         <v>1.1</v>
@@ -15140,13 +15140,13 @@
         <v>2.94</v>
       </c>
       <c r="O76" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P76" t="n">
         <v>1.66</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R76" t="n">
         <v>1.23</v>
@@ -15155,16 +15155,16 @@
         <v>4.4</v>
       </c>
       <c r="T76" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U76" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V76" t="n">
         <v>1.64</v>
       </c>
       <c r="W76" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X76" t="n">
         <v>12.5</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G77" t="n">
         <v>1.92</v>
@@ -15325,7 +15325,7 @@
         <v>3.7</v>
       </c>
       <c r="L77" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M77" t="n">
         <v>1.09</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -15719,10 +15719,10 @@
         <v>1.03</v>
       </c>
       <c r="N79" t="n">
-        <v>2.74</v>
+        <v>6</v>
       </c>
       <c r="O79" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P79" t="n">
         <v>2.74</v>
@@ -15731,10 +15731,10 @@
         <v>1.46</v>
       </c>
       <c r="R79" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="S79" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="T79" t="n">
         <v>1.6</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -15889,13 +15889,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G80" t="n">
         <v>3.5</v>
       </c>
       <c r="H80" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I80" t="n">
         <v>2.8</v>
@@ -15910,7 +15910,7 @@
         <v>1.01</v>
       </c>
       <c r="M80" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N80" t="n">
         <v>2.32</v>
@@ -15925,16 +15925,16 @@
         <v>3.05</v>
       </c>
       <c r="R80" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S80" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="T80" t="n">
         <v>2.38</v>
       </c>
       <c r="U80" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="V80" t="n">
         <v>1.55</v>
@@ -15943,40 +15943,40 @@
         <v>1.4</v>
       </c>
       <c r="X80" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y80" t="n">
         <v>7.2</v>
       </c>
-      <c r="Y80" t="n">
-        <v>7.4</v>
-      </c>
       <c r="Z80" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AA80" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AB80" t="n">
         <v>8.6</v>
       </c>
       <c r="AC80" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD80" t="n">
         <v>15</v>
       </c>
       <c r="AE80" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="AF80" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AG80" t="n">
         <v>17</v>
       </c>
       <c r="AH80" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AI80" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ80" t="n">
         <v>1000</v>
@@ -15985,22 +15985,22 @@
         <v>1000</v>
       </c>
       <c r="AL80" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM80" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN80" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO80" t="n">
-        <v>75</v>
+        <v>340</v>
       </c>
       <c r="AP80" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ80" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR80" t="n">
         <v>13.5</v>
@@ -16009,50 +16009,50 @@
         <v>24</v>
       </c>
       <c r="AT80" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU80" t="n">
         <v>6.2</v>
       </c>
       <c r="AV80" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW80" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX80" t="n">
         <v>17.5</v>
       </c>
       <c r="AY80" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ80" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="BA80" t="n">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="BB80" t="n">
         <v>32</v>
       </c>
       <c r="BC80" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BD80" t="n">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="BE80" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="BF80" t="n">
         <v>36</v>
       </c>
       <c r="BG80" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -16086,7 +16086,7 @@
         <v>2.24</v>
       </c>
       <c r="G81" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H81" t="n">
         <v>3.3</v>
@@ -16101,40 +16101,40 @@
         <v>4</v>
       </c>
       <c r="L81" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M81" t="n">
         <v>1.04</v>
       </c>
       <c r="N81" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O81" t="n">
         <v>1.2</v>
       </c>
       <c r="P81" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R81" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S81" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T81" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="U81" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="V81" t="n">
         <v>1.42</v>
       </c>
       <c r="W81" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X81" t="n">
         <v>23</v>
@@ -16179,34 +16179,34 @@
         <v>20</v>
       </c>
       <c r="AL81" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM81" t="n">
         <v>55</v>
       </c>
       <c r="AN81" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP81" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AQ81" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR81" t="n">
         <v>24</v>
       </c>
       <c r="AS81" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT81" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU81" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV81" t="n">
         <v>13.5</v>
@@ -16227,7 +16227,7 @@
         <v>30</v>
       </c>
       <c r="BB81" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC81" t="n">
         <v>18</v>
@@ -16236,7 +16236,7 @@
         <v>24</v>
       </c>
       <c r="BE81" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF81" t="n">
         <v>10</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
         <v>1.99</v>
       </c>
       <c r="U82" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V82" t="n">
         <v>1.2</v>
@@ -16343,7 +16343,7 @@
         <v>170</v>
       </c>
       <c r="AB82" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC82" t="n">
         <v>8.800000000000001</v>
@@ -16391,7 +16391,7 @@
         <v>18</v>
       </c>
       <c r="AR82" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AS82" t="n">
         <v>44</v>
@@ -16406,7 +16406,7 @@
         <v>20</v>
       </c>
       <c r="AW82" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AX82" t="n">
         <v>8.800000000000001</v>
@@ -16418,7 +16418,7 @@
         <v>21</v>
       </c>
       <c r="BA82" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BB82" t="n">
         <v>15</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -16471,25 +16471,25 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="G83" t="n">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="H83" t="n">
         <v>3</v>
       </c>
       <c r="I83" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="J83" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K83" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="L83" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M83" t="n">
         <v>1.09</v>
@@ -16498,7 +16498,7 @@
         <v>3.15</v>
       </c>
       <c r="O83" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P83" t="n">
         <v>1.67</v>
@@ -16507,134 +16507,134 @@
         <v>2.06</v>
       </c>
       <c r="R83" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S83" t="n">
         <v>3.75</v>
       </c>
       <c r="T83" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="U83" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="V83" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W83" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="X83" t="n">
         <v>1000</v>
       </c>
       <c r="Y83" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD83" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z83" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA83" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC83" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD83" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AE83" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF83" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AG83" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AH83" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AI83" t="n">
         <v>75</v>
       </c>
       <c r="AJ83" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL83" t="n">
         <v>50</v>
       </c>
-      <c r="AK83" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL83" t="n">
-        <v>70</v>
-      </c>
       <c r="AM83" t="n">
         <v>1000</v>
       </c>
       <c r="AN83" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AO83" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP83" t="n">
-        <v>3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ83" t="n">
-        <v>2.46</v>
+        <v>9.6</v>
       </c>
       <c r="AR83" t="n">
-        <v>2.7</v>
+        <v>17.5</v>
       </c>
       <c r="AS83" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.36</v>
+        <v>8.4</v>
       </c>
       <c r="AU83" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV83" t="n">
-        <v>2.58</v>
+        <v>12</v>
       </c>
       <c r="AW83" t="n">
-        <v>2.82</v>
+        <v>4.5</v>
       </c>
       <c r="AX83" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY83" t="n">
-        <v>2.52</v>
+        <v>10</v>
       </c>
       <c r="AZ83" t="n">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="BA83" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="BB83" t="n">
-        <v>2.82</v>
+        <v>4.5</v>
       </c>
       <c r="BC83" t="n">
-        <v>2.8</v>
+        <v>23</v>
       </c>
       <c r="BD83" t="n">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="BE83" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="BF83" t="n">
-        <v>2.74</v>
+        <v>4.3</v>
       </c>
       <c r="BG83" t="n">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -16665,170 +16665,170 @@
         </is>
       </c>
       <c r="F84" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G84" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I84" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J84" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K84" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N84" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q84" t="n">
         <v>3</v>
       </c>
-      <c r="G84" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H84" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="I84" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J84" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K84" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M84" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N84" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O84" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P84" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>2.46</v>
-      </c>
       <c r="R84" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="S84" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="T84" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="U84" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="V84" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W84" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="X84" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="Y84" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z84" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AA84" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AB84" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV84" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC84" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE84" t="n">
+      <c r="AW84" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB84" t="n">
         <v>44</v>
       </c>
-      <c r="AF84" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG84" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH84" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI84" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ84" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK84" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL84" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM84" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN84" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO84" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB84" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BC84" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BD84" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BE84" t="n">
-        <v>1.01</v>
+        <v>190</v>
       </c>
       <c r="BF84" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BG84" t="n">
         <v>1.01</v>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -16868,10 +16868,10 @@
         <v>3.4</v>
       </c>
       <c r="I85" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J85" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="K85" t="n">
         <v>3.75</v>
@@ -16880,7 +16880,7 @@
         <v>1.01</v>
       </c>
       <c r="M85" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N85" t="n">
         <v>2.54</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -17638,55 +17638,55 @@
         <v>1.69</v>
       </c>
       <c r="G89" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H89" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I89" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J89" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="K89" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="L89" t="n">
         <v>1.01</v>
       </c>
       <c r="M89" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N89" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="O89" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="P89" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R89" t="n">
         <v>1.09</v>
       </c>
       <c r="S89" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T89" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U89" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="V89" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W89" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="X89" t="n">
         <v>1000</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -17829,22 +17829,22 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="G90" t="n">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="H90" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I90" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J90" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="K90" t="n">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L90" t="n">
         <v>1.01</v>
@@ -17859,7 +17859,7 @@
         <v>1.02</v>
       </c>
       <c r="P90" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q90" t="n">
         <v>1.53</v>
@@ -17871,112 +17871,112 @@
         <v>1.53</v>
       </c>
       <c r="T90" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U90" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V90" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="W90" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="X90" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y90" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z90" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA90" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB90" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC90" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD90" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE90" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF90" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG90" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH90" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI90" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ90" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK90" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL90" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM90" t="n">
         <v>1000</v>
       </c>
       <c r="AN90" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO90" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AS90" t="n">
         <v>1.01</v>
       </c>
       <c r="AT90" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AU90" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV90" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW90" t="n">
         <v>1.01</v>
       </c>
       <c r="AX90" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY90" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ90" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA90" t="n">
         <v>1.01</v>
       </c>
       <c r="BB90" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC90" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD90" t="n">
         <v>1.01</v>
@@ -17985,14 +17985,14 @@
         <v>1.01</v>
       </c>
       <c r="BF90" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG90" t="n">
         <v>1.01</v>
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -18023,37 +18023,37 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="G91" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H91" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="I91" t="n">
         <v>13</v>
       </c>
       <c r="J91" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="K91" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="L91" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M91" t="n">
         <v>1.05</v>
       </c>
       <c r="N91" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O91" t="n">
         <v>1.25</v>
       </c>
       <c r="P91" t="n">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="Q91" t="n">
         <v>1.81</v>
@@ -18074,7 +18074,7 @@
         <v>1.08</v>
       </c>
       <c r="W91" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="X91" t="n">
         <v>1000</v>
@@ -18086,7 +18086,7 @@
         <v>1000</v>
       </c>
       <c r="AA91" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AB91" t="n">
         <v>1000</v>
@@ -18095,7 +18095,7 @@
         <v>1000</v>
       </c>
       <c r="AD91" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AE91" t="n">
         <v>1000</v>
@@ -18119,7 +18119,7 @@
         <v>1000</v>
       </c>
       <c r="AL91" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM91" t="n">
         <v>1000</v>
@@ -18128,65 +18128,65 @@
         <v>1000</v>
       </c>
       <c r="AO91" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT91" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU91" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AV91" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW91" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX91" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY91" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ91" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA91" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB91" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC91" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD91" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE91" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF91" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG91" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -18432,31 +18432,31 @@
         <v>1.01</v>
       </c>
       <c r="M93" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N93" t="n">
-        <v>2.26</v>
+        <v>2.64</v>
       </c>
       <c r="O93" t="n">
         <v>1.49</v>
       </c>
       <c r="P93" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="R93" t="n">
         <v>1.18</v>
       </c>
       <c r="S93" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T93" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U93" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V93" t="n">
         <v>1.32</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -18808,7 +18808,7 @@
         <v>4.2</v>
       </c>
       <c r="I95" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J95" t="n">
         <v>3.4</v>
@@ -18829,7 +18829,7 @@
         <v>1.37</v>
       </c>
       <c r="P95" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q95" t="n">
         <v>2.1</v>
@@ -18856,7 +18856,7 @@
         <v>15</v>
       </c>
       <c r="Y95" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z95" t="n">
         <v>40</v>
@@ -18865,10 +18865,10 @@
         <v>130</v>
       </c>
       <c r="AB95" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC95" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD95" t="n">
         <v>22</v>
@@ -18910,13 +18910,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ95" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AR95" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS95" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT95" t="n">
         <v>7</v>
@@ -18928,7 +18928,7 @@
         <v>15</v>
       </c>
       <c r="AW95" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX95" t="n">
         <v>10</v>
@@ -18937,10 +18937,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ95" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA95" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB95" t="n">
         <v>20</v>
@@ -18949,20 +18949,20 @@
         <v>19</v>
       </c>
       <c r="BD95" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE95" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF95" t="n">
         <v>12.5</v>
       </c>
       <c r="BG95" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -18996,7 +18996,7 @@
         <v>3.65</v>
       </c>
       <c r="G96" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H96" t="n">
         <v>2.2</v>
@@ -19011,7 +19011,7 @@
         <v>3.5</v>
       </c>
       <c r="L96" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M96" t="n">
         <v>1.1</v>
@@ -19050,7 +19050,7 @@
         <v>12.5</v>
       </c>
       <c r="Y96" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z96" t="n">
         <v>14</v>
@@ -19110,7 +19110,7 @@
         <v>12</v>
       </c>
       <c r="AS96" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT96" t="n">
         <v>10.5</v>
@@ -19125,38 +19125,38 @@
         <v>7.4</v>
       </c>
       <c r="AX96" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY96" t="n">
         <v>14</v>
       </c>
       <c r="AZ96" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA96" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB96" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF96" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BC96" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD96" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE96" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF96" t="n">
-        <v>8.6</v>
       </c>
       <c r="BG96" t="n">
         <v>7.2</v>
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -19208,7 +19208,7 @@
         <v>1.01</v>
       </c>
       <c r="M97" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N97" t="n">
         <v>1.25</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -19408,7 +19408,7 @@
         <v>1.01</v>
       </c>
       <c r="O98" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="P98" t="n">
         <v>1.18</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -19575,31 +19575,31 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="G99" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="H99" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="I99" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J99" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K99" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="L99" t="n">
         <v>1.01</v>
       </c>
       <c r="M99" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N99" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="O99" t="n">
         <v>1.33</v>
@@ -19608,7 +19608,7 @@
         <v>1.71</v>
       </c>
       <c r="Q99" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="R99" t="n">
         <v>1.25</v>
@@ -19623,10 +19623,10 @@
         <v>1.01</v>
       </c>
       <c r="V99" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W99" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="X99" t="n">
         <v>1000</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -19769,19 +19769,19 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="G100" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H100" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I100" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="J100" t="n">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="K100" t="n">
         <v>950</v>
@@ -19793,13 +19793,13 @@
         <v>1.01</v>
       </c>
       <c r="N100" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O100" t="n">
         <v>1.02</v>
       </c>
       <c r="P100" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q100" t="n">
         <v>1.47</v>
@@ -19817,10 +19817,10 @@
         <v>1.01</v>
       </c>
       <c r="V100" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W100" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="X100" t="n">
         <v>1000</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -19963,10 +19963,10 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G101" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="H101" t="n">
         <v>4.1</v>
@@ -19975,16 +19975,16 @@
         <v>5.3</v>
       </c>
       <c r="J101" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K101" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="L101" t="n">
         <v>1.01</v>
       </c>
       <c r="M101" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N101" t="n">
         <v>2.74</v>
@@ -19993,10 +19993,10 @@
         <v>1.37</v>
       </c>
       <c r="P101" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q101" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R101" t="n">
         <v>1.22</v>
@@ -20005,16 +20005,16 @@
         <v>3.5</v>
       </c>
       <c r="T101" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U101" t="n">
         <v>1.01</v>
       </c>
       <c r="V101" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W101" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="X101" t="n">
         <v>1000</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -20157,170 +20157,170 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="G102" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="H102" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="I102" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="J102" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="K102" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L102" t="n">
         <v>1.01</v>
       </c>
       <c r="M102" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N102" t="n">
         <v>3.6</v>
       </c>
       <c r="O102" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="P102" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q102" t="n">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="R102" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S102" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T102" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U102" t="n">
         <v>2.04</v>
       </c>
       <c r="V102" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W102" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="X102" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y102" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z102" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA102" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB102" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC102" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD102" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE102" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF102" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG102" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH102" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI102" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ102" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK102" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL102" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM102" t="n">
         <v>1000</v>
       </c>
       <c r="AN102" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO102" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="AT102" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AU102" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AV102" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="AW102" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX102" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="AY102" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="AZ102" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BA102" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BB102" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BC102" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BD102" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BE102" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BF102" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG102" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -20351,58 +20351,58 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G103" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H103" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I103" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J103" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K103" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L103" t="n">
         <v>1.01</v>
       </c>
       <c r="M103" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N103" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O103" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="P103" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="Q103" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R103" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S103" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="T103" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="U103" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V103" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W103" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X103" t="n">
         <v>14</v>
@@ -20414,7 +20414,7 @@
         <v>28</v>
       </c>
       <c r="AA103" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB103" t="n">
         <v>10.5</v>
@@ -20423,43 +20423,43 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD103" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE103" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF103" t="n">
         <v>17</v>
       </c>
       <c r="AG103" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH103" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI103" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ103" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK103" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL103" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM103" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN103" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AO103" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP103" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AQ103" t="n">
         <v>9.800000000000001</v>
@@ -20468,10 +20468,10 @@
         <v>20</v>
       </c>
       <c r="AS103" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AT103" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU103" t="n">
         <v>6.6</v>
@@ -20480,7 +20480,7 @@
         <v>12.5</v>
       </c>
       <c r="AW103" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AX103" t="n">
         <v>12.5</v>
@@ -20489,32 +20489,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ103" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA103" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BB103" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC103" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD103" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BE103" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF103" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BG103" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -20548,7 +20548,7 @@
         <v>2.38</v>
       </c>
       <c r="G104" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H104" t="n">
         <v>3.4</v>
@@ -20560,7 +20560,7 @@
         <v>3.1</v>
       </c>
       <c r="K104" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L104" t="n">
         <v>1.01</v>
@@ -20578,13 +20578,13 @@
         <v>1.66</v>
       </c>
       <c r="Q104" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R104" t="n">
         <v>1.24</v>
       </c>
       <c r="S104" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="T104" t="n">
         <v>1.95</v>
@@ -20596,7 +20596,7 @@
         <v>1.37</v>
       </c>
       <c r="W104" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X104" t="n">
         <v>12</v>
@@ -20653,10 +20653,10 @@
         <v>70</v>
       </c>
       <c r="AP104" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ104" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR104" t="n">
         <v>17.5</v>
@@ -20665,10 +20665,10 @@
         <v>4.8</v>
       </c>
       <c r="AT104" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU104" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV104" t="n">
         <v>11.5</v>
@@ -20680,10 +20680,10 @@
         <v>11.5</v>
       </c>
       <c r="AY104" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ104" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BA104" t="n">
         <v>4.8</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -20742,19 +20742,19 @@
         <v>2.32</v>
       </c>
       <c r="G105" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="H105" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="I105" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J105" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K105" t="n">
         <v>4.7</v>
-      </c>
-      <c r="J105" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="K105" t="n">
-        <v>4.9</v>
       </c>
       <c r="L105" t="n">
         <v>1.01</v>
@@ -20787,10 +20787,10 @@
         <v>1.01</v>
       </c>
       <c r="V105" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W105" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X105" t="n">
         <v>1000</v>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -20960,19 +20960,19 @@
         <v>1.25</v>
       </c>
       <c r="O106" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P106" t="n">
         <v>1.24</v>
       </c>
       <c r="Q106" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R106" t="n">
         <v>1.18</v>
       </c>
       <c r="S106" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T106" t="n">
         <v>1.01</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -21151,10 +21151,10 @@
         <v>1.01</v>
       </c>
       <c r="N107" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="O107" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="P107" t="n">
         <v>1.39</v>
@@ -21169,16 +21169,16 @@
         <v>5.1</v>
       </c>
       <c r="T107" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U107" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="V107" t="n">
         <v>1.33</v>
       </c>
       <c r="W107" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="X107" t="n">
         <v>10.5</v>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -21321,7 +21321,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G108" t="n">
         <v>1.54</v>
@@ -21330,13 +21330,13 @@
         <v>7</v>
       </c>
       <c r="I108" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J108" t="n">
         <v>4.5</v>
       </c>
       <c r="K108" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L108" t="n">
         <v>1.35</v>
@@ -21345,25 +21345,25 @@
         <v>1.05</v>
       </c>
       <c r="N108" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O108" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P108" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R108" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S108" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T108" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="U108" t="n">
         <v>2.02</v>
@@ -21372,7 +21372,7 @@
         <v>1.14</v>
       </c>
       <c r="W108" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="X108" t="n">
         <v>19</v>
@@ -21405,7 +21405,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH108" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI108" t="n">
         <v>110</v>
@@ -21423,7 +21423,7 @@
         <v>150</v>
       </c>
       <c r="AN108" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO108" t="n">
         <v>120</v>
@@ -21435,10 +21435,10 @@
         <v>23</v>
       </c>
       <c r="AR108" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS108" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT108" t="n">
         <v>8.199999999999999</v>
@@ -21450,7 +21450,7 @@
         <v>24</v>
       </c>
       <c r="AW108" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX108" t="n">
         <v>8.4</v>
@@ -21459,10 +21459,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ108" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA108" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB108" t="n">
         <v>12.5</v>
@@ -21474,17 +21474,17 @@
         <v>29</v>
       </c>
       <c r="BE108" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF108" t="n">
         <v>6.6</v>
       </c>
       <c r="BG108" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -21515,13 +21515,13 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G109" t="n">
         <v>2.36</v>
       </c>
       <c r="H109" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I109" t="n">
         <v>4.3</v>
@@ -21530,7 +21530,7 @@
         <v>3.05</v>
       </c>
       <c r="K109" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L109" t="n">
         <v>1.01</v>
@@ -21575,7 +21575,7 @@
         <v>12.5</v>
       </c>
       <c r="Z109" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA109" t="n">
         <v>110</v>
@@ -21590,7 +21590,7 @@
         <v>17.5</v>
       </c>
       <c r="AE109" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF109" t="n">
         <v>14</v>
@@ -21644,7 +21644,7 @@
         <v>14</v>
       </c>
       <c r="AW109" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX109" t="n">
         <v>11</v>
@@ -21656,29 +21656,29 @@
         <v>18</v>
       </c>
       <c r="BA109" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB109" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC109" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD109" t="n">
         <v>7.8</v>
       </c>
       <c r="BE109" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF109" t="n">
         <v>6.8</v>
       </c>
       <c r="BG109" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -21927,13 +21927,13 @@
         <v>1.01</v>
       </c>
       <c r="N111" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O111" t="n">
         <v>1.29</v>
       </c>
       <c r="P111" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q111" t="n">
         <v>1.29</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
         <v>1.22</v>
       </c>
       <c r="P112" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q112" t="n">
         <v>1.68</v>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-04-04 08:58:46</t>
+          <t>2026-04-04 11:30:42</t>
         </is>
       </c>
     </row>
